--- a/data/Radar_Detecciones.xlsx
+++ b/data/Radar_Detecciones.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas nuevas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las detecciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Alertas nuevas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Todas las detecciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -528,8 +528,1022 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>9990908.529999999</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>manga, manga continua</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>9990908.529999999</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>manga, manga continua</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>contratación por lotes del servicio de dirección facultativa de los trabajos de rehabilitación de colectores de la red de saneamiento integral de acosol, s.a. con manga cipp</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>500991.77</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>cipp, manga</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44160000, 65000000, 71000000, 71500000, 71540000</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=259MiIPtVk7mnwcj%2BxbdTg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>79450913.81</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45232420, 45232421</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EMATSA</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>L'objecte del present contracte son les obres de conservació i manteniment de col·lectors de la xarxa de clavegueram gestionada per EMATSA mitjançant instal·lació de mànega continua autoportant curada in situ (CIPP), d’acord amb les característiques i condicions fixades al plec de prescripcions tècniques regulador d’aquest contracte.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4401808.68</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>cipp, curada in situ</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>45232151</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/f39723ec-587b-4848-b53d-0180e5c0ff0d/300867025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>79450913.81</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>45232420, 45232421</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>EMAYA</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de redacción de proyecto básico de nueva IDAM (Instalación Desaladora de Agua de Mar) y tramitación administrativa de permisos vinculados para EMAYA</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>603300</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71000000, 71311100, 71318000, 71322000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=qt5FN9id8YLIGlsa0Wad%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de redacción del estudio de alternativas, estudios ambientales y anteproyecto de la remodelación de la E.D.A.R. Cerro del Águila (Fuengirola - Mijas) para ACOSOL, S.A.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>490348.91</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71243000, 71300000, 71311000, 71311300, 71322000</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=EFuDWPmaJjQ2wEhQbcAqug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>EMALCSA</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Conservación, reparación y mantenimiento de las infraestructuras de agua y alcantarillado gestionadas por Emalcsa</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>4683636.14</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45112100, 45232150, 50000000, 65100000, 90400000</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=M48%2BHjPpqKeExvMJXBMHHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Santa María de la Alameda. Fase I (PLAN SANEA 2500)”. CYII 2026/24</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>5244670.28</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-santa-maria-alameda</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Fresnedillas de la Oliva. Fase I (PLAN SANEA 2500)”. CYII 2026/11</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>3310312.26</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-fresnedillas-oliva</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1143886.29</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1143886.29</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Suministro de permanganato potásico para ETAP en la Delegación de Cáceres</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>26980</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>24314100</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/suministro-permanganato-potasico-etap-delegacion-caceres</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Empresa Municipal de Aguas de Gijón</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Obras de renovación del colector de saneamiento en la Avenida Príncipe de Asturias, entre las calles Guatemala y Brasil (Gijón)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>440676.07</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232400, 45232440</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=SnbVn%2Fo5sgGopEMYCmrbmw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>NILSA</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>320078.64</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>SCPSA — Servicios de la Comarca de Pamplona</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Colectores de pluviales en Pza. Valle de Aranguren de Mutilva (RM282370_01)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>185937.04</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>45232440</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=3167&amp;Ticket=2608142133474FAF3BB0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>NILSA</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>320078.64</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -540,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -628,11 +1642,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -651,21 +1665,21 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Servicio de diseño, fabricación, suministro e instalación para la rehabilitación mediante manga de los colectores del saneamiento integral, tramo Marbella–Estepona (Lote 1)</t>
+          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4030000</v>
+        <v>9990908.529999999</v>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>manga</t>
+          <t>manga, manga continua</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -675,74 +1689,82 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>90400000</t>
+          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Águas e Energia do Porto</t>
+          <t>ACOSOL</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+          <t>contratación por lotes del servicio de dirección facultativa de los trabajos de rehabilitación de colectores de la red de saneamiento integral de acosol, s.a. con manga cipp</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2100000</v>
+        <v>500991.77</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>sem vala</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>cipp, manga</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>44160000, 65000000, 71000000, 71500000, 71540000</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu/</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=259MiIPtVk7mnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -756,16 +1778,16 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AQUAVALL</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>180000</v>
+        <v>79450913.81</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -773,7 +1795,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>PUB</t>
@@ -781,60 +1807,5724 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71322000</t>
+          <t>45232420, 45232421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>EMATSA</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>L'objecte del present contracte son les obres de conservació i manteniment de col·lectors de la xarxa de clavegueram gestionada per EMATSA mitjançant instal·lació de mànega continua autoportant curada in situ (CIPP), d’acord amb les característiques i condicions fixades al plec de prescripcions tècniques regulador d’aquest contracte.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>4401808.68</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>cipp, curada in situ</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45232151</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/f39723ec-587b-4848-b53d-0180e5c0ff0d/300867025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EMAYA</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de redacción de proyecto básico de nueva IDAM (Instalación Desaladora de Agua de Mar) y tramitación administrativa de permisos vinculados para EMAYA</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>603300</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>71000000, 71311100, 71318000, 71322000</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=qt5FN9id8YLIGlsa0Wad%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de redacción del estudio de alternativas, estudios ambientales y anteproyecto de la remodelación de la E.D.A.R. Cerro del Águila (Fuengirola - Mijas) para ACOSOL, S.A.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>490348.91</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>71243000, 71300000, 71311000, 71311300, 71322000</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=EFuDWPmaJjQ2wEhQbcAqug%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>EMALCSA</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Conservación, reparación y mantenimiento de las infraestructuras de agua y alcantarillado gestionadas por Emalcsa</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>4683636.14</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>45112100, 45232150, 50000000, 65100000, 90400000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=M48%2BHjPpqKeExvMJXBMHHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Santa María de la Alameda. Fase I (PLAN SANEA 2500)”. CYII 2026/24</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5244670.28</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-santa-maria-alameda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Fresnedillas de la Oliva. Fase I (PLAN SANEA 2500)”. CYII 2026/11</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3310312.26</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-fresnedillas-oliva</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1143886.29</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Suministro de permanganato potásico para ETAP en la Delegación de Cáceres</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>26980</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24314100</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/suministro-permanganato-potasico-etap-delegacion-caceres</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Empresa Municipal de Aguas de Gijón</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Obras de renovación del colector de saneamiento en la Avenida Príncipe de Asturias, entre las calles Guatemala y Brasil (Gijón)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>440676.07</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232400, 45232440</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=SnbVn%2Fo5sgGopEMYCmrbmw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>NILSA</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>320078.64</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>SCPSA — Servicios de la Comarca de Pamplona</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Colectores de pluviales en Pza. Valle de Aranguren de Mutilva (RM282370_01)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>185937.04</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>45232440</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=3167&amp;Ticket=2608142133474FAF3BB0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ACUAES</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Ejecución de las obras del "Proyecto actualizado del abastecimiento de agua a Jaca, TT.MM. de Villanúa, Castiello de Jaca y Jaca (Huesca)" y su "Adenda 06/24"</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>6589764.84</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45231100, 45231300, 45240000</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Pp2GXUPs%2BC47u6%2B%2FR7DUoA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>EMASESA</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto para la renovación de las redes de abastecimiento y saneamiento en Avda. de la Reina Mercedes. Distrito Bellavista- La Palmera, Sevilla.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>4408429.38</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bJ7RafCEkY6cCF8sV%2BqtYA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>EMACSA</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio para la ejecución de actuaciones integrales de mantenimiento, mejora y conservación de infraestructuras del ciclo integral del agua gestionadas por EMACSA.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>32094518.03</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>45232150, 45232151, 50532000, 50800000, 90400000</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zZBMviMwMpEeC9GJQOEBkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de asistencia técnica y coordinación de seguridad y salud para la supervisión y control del desarrollo de las obras del “proyecto de construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)”</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>350174459</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>71310000, 71311100</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-coordinacion-seguridad-salud-supervision-control-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de asistencia técnica para la redacción de proyectos y pliegos de estaciones de tratamiento de agua (Potable, Residual y Regenerada)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71242000, 71300000, 71311000, 71330000</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-pliegos-estaciones-tratamiento-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Obras de mejora de Redes de Saneamiento gestionadas por Canal de Isabel II, S.A., M.P. – PLAN SANEA 2</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>214220312.18</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-mejora-redes-saneamiento-gestionadas-canal-isabel-ii-sa-mp-plan-sanea-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de asistencia técnica para la redacción de proyectos de infraestructuras hidráulicas y aprovechamientos energéticos</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>71242000, 71300000, 71311000, 71330000</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-infraestructuras-hidraulicas-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de conservación y mantenimiento de las redes de saneamiento periférico gestionadas por Canal de Isabel II, S.A., M.P.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>285736930.5</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>50000000, 90400000</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-conservacion-mantenimiento-redes-saneamiento-periferico-gestionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>AGUASVIRA</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de limpieza de la red e instalaciones de saneamiento gestionadas por la empresa Aguasvira</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1897500</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>90400000, 90470000, 90513600, 90513700</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2F9%2BLOFDQWW7N3k3tjedSGw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ACUAES</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Ejecución de las obras del Proyecto "Obras y actuaciones para la mejora de las instalaciones del sistema de abastecimiento del Valle Esgueva (Valladolid)".</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2187973.19</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>45213260, 45232150, 45252126</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HOwdh03hNTSOUi78BmzhOQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ESAMUR</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Estación depuradora de aguas residuales de Cañadas de San Pedro (Murcia)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2395990.69</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>45232420, 45232430</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=56qhfPOd%2Fw%2FIGlsa0Wad%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>L’objecte del present contracte és l’execució de les obres de manteniment i reparació per a corregir i millorar les condicions d’explotació d’alguns dipòsits de la Zona sud d’ATL, elegits segons la rellevància dels esmentats informes, a excepció d’aquells dipòsits on a l’actualitat s’hi estan duen a terme o hi ha previst actuacions especifiques de renovació o manteniment, o bé que per diferents circumstancies el termini d’execució dels treballs es superior al temps que el dipòsit en qüestió pot estar sense prestar el servei.
+Els dipòsit a rehabilitar estan situats al termes municipals de: Òdena, Moja, Avinyonet del Penedès, Piera, Sant Esteve Sesrovires, Masquefa, Sant Andreu de la Barca, Castellbisbal, Pallejà, Rubí, Sabadell, Sant Quirze del Vallès i Castellar del Vallès.
+Els treballs a realitzar són específics per a cada dipòsit i estan descrits detalladament al projecte constructiu corresponent.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>3161756.55</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/2cd3edde-16d5-4278-931d-968d40ffb17f/300859539</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>EMAYA</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Renovación red de agua potable y saneamiento en zona C/Saridakis</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>992163.92</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>45232150, 45232410</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Q%2B3PBn4BGMdVq4S9zvaQpQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Aigües de Manresa</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
+La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
+Aquesta exigència es justifica per les característiques singulars de l'actuació projectada, atès que les obres s'han d'executar de forma coordinada amb les obres del nou col·lector de Salmorres i de la impulsió d'aigua regenerada actualment en execució, compartint traçat, accessos, ocupacions temporals, servituds i zones de treball.
+La correcta elaboració de les ofertes requereix que els licitadors coneguin directament l'estat actual dels terrenys, les condicions reals d'accés, les limitacions derivades de la coexistència amb les obres en curs i els condicionants que poden afectar la planificació i execució dels treballs.
+Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>856364.91</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>45231110, 45232400, 45232410, 45232411</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300862918</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de asistencia técnica para la redacción de documentos normativos, proyectos en las instalaciones de las presas de Canal de Isabel II, S.A. M.P. y estudios técnicos de cantidad y calidad del recurso en los embalses y masas de agua de la Comunidad de Madrid</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>71311000</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-documentos-normativos-proyectos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>EMASESA</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto de sustitución de las redes de abastecimiento, saneamiento e instalación de nueva red de baldeo de la Calle Vírgenes, por conservación. Distrito Casco Antiguo, Sevilla.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>707098.53</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=TkvLlQXSzqq2gkLQ8TeYKA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Empresa Municipal de Aguas de Gijón</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Obras de reposición de las redes de abastecimiento y saneamiento afectadas por la rehabilitación de viviendas degradadas de la Obra Sindical de Contrueces (Fase I)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>350200.9</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232150</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=llLPwmCsTj4mMOlAXxDEjw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Aguas de Cádiz</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de infraestructura hidráulica en Calle General Luque</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>193779.79</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>43328000, 45231300, 45232150, 45232400, 45232410</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RDQDicCcUYPi0Kd8%2Brcp6w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Contratación del Servicio de "Redacción de proyectos, Dirección Facultativa y asistencia a la legalización de las instalaciones de protección contra incendios en diversas estaciones depuradoras de aguas residuales (EDARs) de ACOSOL"</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>71000000, 71240000, 71520000</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RXW343uwBxCkU02jNGj1Fw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Consorcio de Aguas Bilbao Bizkaia</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Obras de saneamiento en el barrio de Eleizondo en el término municipal de Zeanuri</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>275503.79</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso616572/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>MARE</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de gestión de lodos de EDAR producidos en la Red de Saneamiento de Cantabria</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>4089020.27</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>90513700, 90513800</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DlbLIjNtKBaKeVWTb9Scog%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Contratación del servicio de consultoría y asistencia técnica para la redacción del proyecto de ejecución, dirección de obra y coordinación de seguridad y salud de la reforma del campo de fútbol y pista de atletismo del estadio de Berazubi y nuevo edificio de gimnasios.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>96600</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>71000000</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso736330/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de servicios de redacción del proyecto básico y de ejecución, dirección facultativa de las obras y coordinación en materia de seguridad y salud de las obras de realización de una pista de atletismo de 200 metros en el municipio de Almussafes</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>39495.6</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>71000000, 71520000</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XL%2BNTyDcCyWHCIsjvJ3rhQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>MARE</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Drenaje de aguas procedentes de los desbordamientos de la acequia Mare y Barranco de Sotaia en suelo no urbanizable que entran en suelo urbanizable con ordenación pormenorizada Sector D</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>40377.8</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>45232440</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zo5cUizKxC5VYjgxA4nMUw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Obras de renovación de tuberías de abastecimiento en urbanizaciones</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>2892150</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>45231110</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-tuberias-abastecimiento-urbanizaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 67/2026 “Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>2580718.9</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>71310000, 71311100</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>EMAYA</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>El objeto de este procedimiento es establecer las condiciones técnicas y económicas para el suministro de recambios eléctricos y mecánicos de los diferentes equipos que tiene instalados EMAYA en sus estaciones de impulsión.</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>31210000, 38420000, 42124200, 42996000</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XiV6iUa%2F7v4aF6cS8TCh%2FA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Metro de Madrid, S.A.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Acuerdo marco para el suministro de mangas neumáticas destinadas al mantenimiento de los trenes del material móvil e instalaciones de Metro Madrid</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>430000</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>44165000, 44165100, 44165300</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/acuerdo-marco-suministro-mangas-neumaticas-destinadas-mantenimiento-trenes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de renovación de la red de saneamiento en el municipio de Santa María de la Alameda. Fase I (Plan Sanea 2500)” CYII 2026/25</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>231900</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>71310000, 71311000, 71311100, 71520000</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/asistencia-tecnica-realizacion-trabajos-vigilancia-control-coordinacion-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Chapinería. Fase I CYII 2026/15</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>231900</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>71310000, 71311000, 71311100, 71520000</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-realizacion-trabajos-vigilancia-control-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 53/2026 "Obras de renovación de tuberías de abastecimiento en urbanizaciones"</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>287158.38</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>71310000, 71311100</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Obras de renovación de la red de abastecimiento y saneamiento en la ciudad de Cáceres en las zonas: Barriada de San Blas, Calle Moreras, Camberos y Callejón de Trujillo</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>341928.01</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>45231110</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-abastecimiento-saneamiento-ciudad-caceres-zonas-barriada-san</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Pleno del Ayuntamiento de Fortuna</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Concesión del servicio público de abastecimiento de agua potable y alcantarillado del municipio de Fortuna</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>68949530.8</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>65111000, 65130000, 90480000</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RCFijR8b%2BYmcTfjQf3USOg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Junta de Gobierno Local del Ayuntamiento de Pollença</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de servicios de mantenimiento y operación del servicio de alcantarillado del municipio de Pollença (Illes Balears)</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>2139325.94</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>50510000, 90400000, 90470000, 90480000, 90491000</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=1e36YO6YJeHL1rX3q%2FMAPA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>La ejecución de las obras comprendidas en el proyecto de “OBRAS DE SANEAMIENTO EN LA ZONA COSTERA DE ARICO”, t.m. de Arico, redactado por la empresa CIVICA INGENIEROS, S.L, que contempla varias actuaciones en la red de saneamiento del municipio de Arico, seleccionadas de entre las medidas contenidas en el documento “Diagnóstico y Propuestas de Actuación en materia de Saneamiento".</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1816937.94</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DY9ZQkWH0O%2BLAncw3qdZkA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>"Red de Alcantarillado del ámbito de La Bastona", T.M.  de Santa Úrsula</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>2057453.5</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232130, 45233252</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vQGQvWXwPLudkQsA7ROvsg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Junta de Gobierno del Ayuntamiento de Cádiz</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Suministros necesarios para la celebración del Festival Manga de Cádiz FEMANCA 2026 (4 LOTES)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>58016</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>30236000, 31211100, 31527200, 32320000, 35111300</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3NalfqN%2FH1zzAq95uGTrDQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>774510.76</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>45232440</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=V9R23eu82UwIYE3ZiZ%2BxmQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Puçol</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Obras 1ª fase del colector unitario de la C/Alicante en Puçol.</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>939454.59</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=WKz%2F6IjRhlfXOjazN1Dw9Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Ajuntament de Sant Feliu de Guíxols</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>El objeto del presente contrato es la prestación del servicio de mantenimiento, conservación, inspección y limpieza de la red de alcantarillado del término municipal de Sant Feliu de Guíxols. Dentro del servicio de mantenimiento se incluyen las tareas de inspección, limpieza y conservación de la red, así como la construcción de las acometidas de terceros a la mencionada red y el mantenimiento de las acometidas de los edificios de responsabilidad municipal, restante fuera de este contrato el mantenimiento de las redes de alcantarillado de cualquier otro organismo y de las acometidas de los edificios particulares.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>1016373.82</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>45232410, 90480000</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/6d8b7d9f-f3b1-48bc-889b-e6e04bacaf5e/300866915</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Consorcio Urbanístico Leganés Tecnológico</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>LGT_2026_CO_01 Proyecto constructivo e incoación del procedimiento de contratación de las obras de finalización del colector desdoblado del arroyo Butarque en el ámbito del PP-2, centro, del Plan de Sectorización Autovía Toledo Norte del Plan General de Ordenación Urbana de Leganés (MADRID), EXPEDIENTE CO/01/2026</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>784673.0699999999</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>45232440</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/lgt2026co01-proyecto-constructivo-e-incoacion-procedimiento-contratacion-obras</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Narón</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Ampliacion da rede de saneamento en A Rocha (Sedes), comprendida no Plan provincial de cooperación ás obras e servizos de competencia municipal (Plan único de concellos) POS+Adicional 2/2025</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>384003.04</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>44162500, 45232400, 45232410</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=GFxBe4DrBfvL1rX3q%2FMAPA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Agüimes</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Mejora y Optimización Red de Abastecimiento de Agua de Temisas</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>599625.8</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OxfluKxhWGV6nTs9LZ9RhQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Consejería de Industria, Energía, Ciencia y Territorio</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>OBRAG26003 Nuevo colector en Rena (Badajoz)</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>395041.32</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FgAgNDFSE7aKeVWTb9Scog%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de la Histórica Villa de los Realejos</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Contratación de obras del proyecto de "Remodelación del entorno urbano y adecuación de la red de abastecimiento en la urbanización Los Príncipes (Fase I)"</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>517249.41</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>45232150, 45233222</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=VQOMAmLOSzeS81gZFETWmA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Consejo de Administración de Limpieza y Mantenimiento de Carmona, S.L.U.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Obras de rehabilitación de pavimentos y renovación de las redes de alcantarillado y abastecimiento de agua potable en la Barriada de Guadajoz. Fase 1</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>423938.36</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>45232100, 45232150, 45232400, 45232410, 45233252</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bCgfi8hy24h9PLkba5eRog%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Presidencia de la Confederación Hidrográfica del Miño-Sil</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto de colectores de la red de fecales de la calle Plácido Peña. T.M. de Vilalba (Lugo) PDM MIÑO-SIL ES010_2_ALCH0SBET29UR2023</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>675986.95</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=0sPmJ1%2FV1fD%2Fa9DgO%2BoYKQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Salamanca</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Obras de Renovación de la red de distribución de agua potable en varias calles de los barrios San Cristóbal, San Esteban y Fontana y en Pizarrales Norte.</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>538921.6899999999</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45233200</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Nzb4BMmgaFfIGlsa0Wad%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Cervo</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Renovación beirarrúas e rede de saneamento da avenida da Mariña, en San Ciprián</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>458620.35</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>45232410, 45233200, 45233252</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hQUN1x2ScH%2BLAncw3qdZkA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Ibdes</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>El proyecto de "MEJORA DE SERVICIOS Y DE PAVIMENTOS" en Ibdes, tiene por objeto diversas obras de mejora de pavimentos y de las conducciones del alcantarillado y de distribución de agua en varios tramos de las Calles Rúa y Cerro de San Lorenzo.</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>346698.53</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>45232150, 45232400, 45233252</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HF9AC8k%2B%2F3mqb7rCcv76BA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>La contratación de la ejecución de las obras de pavimentación y renovación de redes calle Agustina de Aragón números 58 a 76 y adyacentes (Fase 1) y calle Agustina de Aragón números 38 a 56 y calle La Huerta núm. 1 a 9 (Fase 2)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>545400.61</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>45231221, 45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OvOki5I9GBJrSd8H4b2soA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Las obras de pavimentación y renovación de redes</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>545400</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>45231221, 45231300, 45233252</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=38evUZBxaXWHCIsjvJ3rhQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Ejecución de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>533872.4</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>45232440, 45240000</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HnzMWLjwbK%2B8ebB%2FXTwy0A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>AGASA-Consejo de Administración</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Obras de instalación de la cuarta bomba de la EBAR Santa Catalina en la red de saneamiento de AGASA</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>465242.86</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>45232152</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso733199/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Artziniega-Pleno</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega (Fase 1)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>567293.62</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso31125/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Basauri-Alcalde</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Obra de reposición del muro y la red de saneamiento en la trasera de la calle Luis Petralanda 1-3 de Basauri.</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>469741.46</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso725833/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Dirección Gerente de Aguas Vega Sierra Elvira, S.A.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de la red de abastecimiento de las calles Salitre, Vicente Aleixandre y Málaga, y la red de saneamiento de estas dos últimas, de Atarfe (Granada).</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>234044.63</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>44160000, 45200000, 45220000, 45231100, 45232100</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=cTWFE5D8Zh5VkTabT%2FRM8A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Carballo</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de obras: Red de abastecimiento de agua potable desde el lugar de Almacén al lugar de Vilar de Francos, en la parroquia de Artes (OBR 06/2026) incluída en el POS+Adicional 4/2025, 2ª Fase</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>247592.94</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>45200000, 45231000, 45231300, 45232150</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=meSIPtE5fKQ7%2B9FIQYNjeQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Aena. Dirección del Aeropuerto Adolfo Suárez Madrid-Barajas</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto Y Obra Acometida Red De Saneamiento Parcela Supermercado Aeroportuario</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>206300</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=k1WCTiBaoektm4eBPtV6eQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Presidencia de la Autoridad Portuaria de la Bahía de Algeciras</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto de desvio del ramal norte de la red de abastecimiento del área portuaria de Campamento</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>287137.15</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232150</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=lc5tGIAbOAjmnwcj%2BxbdTg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Hinojosa del Duque</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Renovación del pavimento y red de saneamiento y agua potable de la Plaza Duque de Béjar de Hinojosa del Duque.</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>314890.08</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>45220000, 45232410, 45233251, 45233252</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=tomlDPx2VWQmMOlAXxDEjw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Pleno del Ayuntamiento de Torralba de Ribota</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Obras de pavimentado de calles y renovación de redes en el término municipal de TORRALBA DE RIBOTA</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>192375.91</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>45111100, 45232400, 45233252, 45330000</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=H%2F59EKurpZ1SYrkJkLlFdw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Pleno del Ayuntamiento de Cretas</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto de acondicionamiento y renovación de conducción de abastecimiento de agua</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>118205.83</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FNDtn0ZSI8RxseVhcqrkhw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Entidad Pública Empresarial Local Centros de Arte, Cultura y Turismo de Lanzarote</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Obra de nueva EBAR y tubería de impulsión en La Cueva de los Verdes</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>102536.2</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232411, 45232440</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vwVlLdPv92qcCF8sV%2BqtYA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de tubería de distribución en el vial público C/ Vicent Serra y actuaciones complementarias en el sistema de abastecimiento urbano de Sant Miquel de Balansat</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>96500.2</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=c3vjWc0VQQ0aF6cS8TCh%2FA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de tubería de distribución en Plaza España y Calle Mossèn Vicent Ferrer i Guasch, con actuaciones complementarias en el sistema de abastecimiento urbano de Sant Joan de Labritja</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>125890</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=2yr%2BUKjzV%2BGFlFRHfEzEaw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Xunta de Goberno Local del Ayuntamiento de Boiro</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Contratación para a execución da obra de Renovación de tramo de tubería de impulsión á estación de tratamento de auga potable (ETAP) de Boiro, mediante procedemento aberto e TRAMITACIÓN ANTICIPADA (DA 3.2 LCSP) vinculada subvención solicitada Augas de Galicia (DOG número 90 do 18 de maio de 2025) cofinanciada fondos FEDER programa 2021-2027(código proc. AU301E)</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>79632.66</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=g3pTkEh1QTyS81gZFETWmA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Cáceres</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Renovación en la Red de Saneamiento de tramo en Calles Islas Baleares, Pedro Romero Mendoza y Arsenio Gallego, Recrecido de Pozos de Saneamiento en Parcela Municipal y Renovación de Acometida de Saneamiento del Camping Municipal de Cáceres.</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>82975.21000000001</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=nVZ97Q1pak%2FkY6rls5tG9A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Villablino</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de obra de renovación de red de abastecimiento y aceras de la Calle Leitariegos en Villablino</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>147377.86</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>45232150, 45233222</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2Fcvza%2BgevtBWhbmkna2nXQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Alginet</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de la red de alcantarillado de la urbanización San Patricio d'Alginet (Fase I)</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>150364.75</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>45200000, 45231300, 45232150, 45232400, 45232410</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=74A3N79XrwAeC9GJQOEBkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Miengo</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de la Red General de Abastecimiento en Avenida de Los Menicenses de Miengo en término municipal de Miengo</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>80603.17</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FfuggmFUPMKAAM7L03kM8A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Junta de Gobierno Local del Ayuntamiento de Alcalà de Xivert</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Obras de mejoras hidráulicas en la red de saneamiento de Alcalà de Xivert-Alcossebre</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>100541.82</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=a%2FsgtfkOGkAUqXM96WStVA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Consejería Insular de Área de Cooperación Municipal y Vivienda del Cabildo Insular de Tenerife</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>El objeto del contrato de servicios será la REDACCIÓN DEL PROYECTO y DIRECCIÓN DE LA OBRA denominada "REFORMA DE LA RED DE SANEAMIENTO DE LA CALETA DE INTERIÁN, FASE II", en el municipio de Garachico, incluidas en el Plan Insular de Cooperación a las obras y servicios de competencia municipal 2022-2026.</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>99971.42</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>71000000, 71240000</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=P0CRmBEuH2%2Fmnwcj%2BxbdTg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Junta de Gobierno Local del Ayuntamiento de Consell</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de obras de renovación de la red de agua potable y mejora del firme del camino de Son Biel.</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>107187.43</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>45232100, 45232150</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=ea7jddmClrhVq4S9zvaQpQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Baena</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Obras de mejora y ampliación de la red de saneamiento de la calle Matadero y confluencias de Avda Cañete de las Torres, calle Demetrio de los Ríos y calle Sargento Domingo Argudo.</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>69567.39999999999</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>45112000, 45232400, 45232410</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=iNYtiIP2jyQeC9GJQOEBkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Comisión ejecutiva del Consejo de Administración de la Empresa Municipal de Transportes de Fuenlabrada, S.A.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Obras para la mejora integral de la red de saneamiento interior y construcción de un aseo auxiliar exterior en la campa de la EMTF</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>102721.88</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>45215500, 45232400, 45232410, 45233252</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=eVV8%2BC8olRV4zIRvjBVCSw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Área de Fomento de la Diputación Provincial de Badajoz</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Asistencia técnica para la redacción del proyecto de ejecución, dirección de obras y coordinación de seguridad y salud, por lotes, para las obras de  mejora red de abastecimiento en varias localidades de la provincia de Badajoz. Cofinanciado al 85% por FEDER a través del Programa Plurirregional de España 2021-2027</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>112019.15</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>71310000</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=By3FKGFakezVGIpKDxgsAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldia del Ayuntamiento de Argamasilla de Calatrava</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Mejora de la red de abastecimiento de agua potable en el municipio de Argamasilla de Calatrava.</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>88836.67999999999</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=16Y%2BH5iLq9GP%2Bo96UAV7cQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Valdemorales</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Ejecución de las obras correspondientes exclusivamente a la fase 1 conducción general del proyecto general de "modernización de la red de abastecimiento del municipio de  Valdemorales (Cáceres)</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>44037.27</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>45231300, 45232150, 45233200, 45240000, 45252126</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=blNQxGZAd9JJ8Trn0ZPzLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Dirección de las obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>61960.86</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>71300000, 71322000, 71520000</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=MCV%2BAUHsDWnCfVQHDepjGQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Dirección de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>44610.5</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>71300000, 71322000, 71520000</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=F%2FUx5m7rtlu8ebB%2FXTwy0A%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de La Solana</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Obras de Renovación de redes de abastecimiento en Calle Molinos de Viento, de La Solana (Ciudad Real)</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>61709.77</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hwqCatsJl8gS7pcxhTeWOg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Ente Público Empresarial Augas de Galicia</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>AUG-2026-0032: Obra de ampliación y mejora de la red de saneamiento integral del municipio. Saneamiento del Camino de la Torroeira. Parroquia de Louredo. Mos (Pontevedra). Actuación cofinanciada por la Unión Europea con el Fondo Europeo Agrícola de Desarrollo Rural (Feader) en un 60% del gasto elegible en el marco del Plan estratégico de la política agrícola común 2023_2027 (PEPAC) en Galicia.</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>63904.44</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratosdegalicia.gal/licitacion?N=827669</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Comisión Permanente de la Mancomunidad de Valdizarbe - Izarbeibarko Mankomunitatea</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Obras de renovación del colector de saneamiento de la Calle Santa María (campo de fútbol) en Obanos</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>51496.63</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>45112000, 45231300, 45232410, 45233252</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=8086&amp;Ticket=2608261225566A4631E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Presidencia de la Mancomunidad de Mairaga</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto y dirección facultativa de la obra de Pavimentación y renovación de redes de calles Barranco Salado, La Estanca y Bardenas Reales de Caparroso</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>43017.16</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>71240000</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2608031429198E3AD3EC</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Junta de Gobierno Local del Ayuntamiento de Baztan</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>conexión a la red de saneamiento del barrio de Etxerri de Gartzain en el municipio de Baztan</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>41206.09</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>45231100, 45232150</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2607211228565F80EFF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Portugalete -Alcalde</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Asistencia técnica para la redacción del proyecto de renovación del colector H de la calle Miralrío de Portugalete.</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>71242000</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso702799/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Artziniega-Alcalde</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Redacción del Proyecto y Dirección Facultativa para las obras de renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega- Fase II</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>19355</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>71240000</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso398838/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B104" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ACOSOL</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de diseño, fabricación, suministro e instalación para la rehabilitación mediante manga de los colectores del saneamiento integral, tramo Marbella–Estepona (Lote 1)</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>4030000</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>90400000</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Águas e Energia do Porto</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>sem vala</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>AQUAVALL</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>71322000</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>SIMAS de Oeiras e Amadora</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G107" s="3" t="n">
         <v>890000</v>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>https://www.base.gov.pt/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Radar_Detecciones.xlsx
+++ b/data/Radar_Detecciones.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Todas las detecciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -528,1022 +528,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>ACOSOL</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>9990908.529999999</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>manga, manga continua</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>ACOSOL</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>9990908.529999999</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>manga, manga continua</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ACOSOL</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>contratación por lotes del servicio de dirección facultativa de los trabajos de rehabilitación de colectores de la red de saneamiento integral de acosol, s.a. con manga cipp</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>500991.77</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>cipp, manga</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>44160000, 65000000, 71000000, 71500000, 71540000</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=259MiIPtVk7mnwcj%2BxbdTg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>79450913.81</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45232420, 45232421</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>EMATSA</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>L'objecte del present contracte son les obres de conservació i manteniment de col·lectors de la xarxa de clavegueram gestionada per EMATSA mitjançant instal·lació de mànega continua autoportant curada in situ (CIPP), d’acord amb les característiques i condicions fixades al plec de prescripcions tècniques regulador d’aquest contracte.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4401808.68</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>cipp, curada in situ</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>45232151</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://contractaciopublica.cat/ca/detall-publicacio/f39723ec-587b-4848-b53d-0180e5c0ff0d/300867025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>79450913.81</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>45232420, 45232421</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>EMAYA</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de redacción de proyecto básico de nueva IDAM (Instalación Desaladora de Agua de Mar) y tramitación administrativa de permisos vinculados para EMAYA</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>603300</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>ADJ</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71000000, 71311100, 71318000, 71322000</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=qt5FN9id8YLIGlsa0Wad%2Bw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>ACOSOL</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de redacción del estudio de alternativas, estudios ambientales y anteproyecto de la remodelación de la E.D.A.R. Cerro del Águila (Fuengirola - Mijas) para ACOSOL, S.A.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>490348.91</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>71243000, 71300000, 71311000, 71311300, 71322000</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=EFuDWPmaJjQ2wEhQbcAqug%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>EMALCSA</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Conservación, reparación y mantenimiento de las infraestructuras de agua y alcantarillado gestionadas por Emalcsa</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>4683636.14</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EV</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45112100, 45232150, 50000000, 65100000, 90400000</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=M48%2BHjPpqKeExvMJXBMHHQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Santa María de la Alameda. Fase I (PLAN SANEA 2500)”. CYII 2026/24</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>5244670.28</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-santa-maria-alameda</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Fresnedillas de la Oliva. Fase I (PLAN SANEA 2500)”. CYII 2026/11</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>3310312.26</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-fresnedillas-oliva</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1143886.29</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1143886.29</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Suministro de permanganato potásico para ETAP en la Delegación de Cáceres</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>26980</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24314100</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/suministro-permanganato-potasico-etap-delegacion-caceres</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Empresa Municipal de Aguas de Gijón</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Obras de renovación del colector de saneamiento en la Avenida Príncipe de Asturias, entre las calles Guatemala y Brasil (Gijón)</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>440676.07</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>45231300, 45232400, 45232440</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=SnbVn%2Fo5sgGopEMYCmrbmw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>NILSA</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>320078.64</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EV</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>45231300, 45233252</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>SCPSA — Servicios de la Comarca de Pamplona</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Colectores de pluviales en Pza. Valle de Aranguren de Mutilva (RM282370_01)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>185937.04</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>ADJ</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>45232440</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=3167&amp;Ticket=2608142133474FAF3BB0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>NILSA</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>320078.64</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>45231300, 45233252</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1554,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3032,7 +2018,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3283,7 +2269,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -3297,22 +2283,26 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>EMASESA</t>
+          <t>Aigües de Manresa</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de sustitución de las redes de abastecimiento, saneamiento e instalación de nueva red de baldeo de la Calle Vírgenes, por conservación. Distrito Casco Antiguo, Sevilla.</t>
+          <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
+La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
+Aquesta exigència es justifica per les característiques singulars de l'actuació projectada, atès que les obres s'han d'executar de forma coordinada amb les obres del nou col·lector de Salmorres i de la impulsió d'aigua regenerada actualment en execució, compartint traçat, accessos, ocupacions temporals, servituds i zones de treball.
+La correcta elaboració de les ofertes requereix que els licitadors coneguin directament l'estat actual dels terrenys, les condicions reals d'accés, les limitacions derivades de la coexistència amb les obres en curs i els condicionants que poden afectar la planificació i execució dels treballs.
+Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>707098.53</v>
+        <v>856364.91</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -3322,12 +2312,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45231110, 45232400, 45232410, 45232411</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=TkvLlQXSzqq2gkLQ8TeYKA%3D%3D</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300863597</t>
         </is>
       </c>
     </row>
@@ -3338,7 +2328,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -3352,33 +2342,41 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Empresa Municipal de Aguas de Gijón</t>
+          <t>Aigües de Manresa</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Obras de reposición de las redes de abastecimiento y saneamiento afectadas por la rehabilitación de viviendas degradadas de la Obra Sindical de Contrueces (Fase I)</t>
+          <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
+La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
+Aquesta exigència es justifica per les característiques singulars de l'actuació projectada, atès que les obres s'han d'executar de forma coordinada amb les obres del nou col·lector de Salmorres i de la impulsió d'aigua regenerada actualment en execució, compartint traçat, accessos, ocupacions temporals, servituds i zones de treball.
+La correcta elaboració de les ofertes requereix que els licitadors coneguin directament l'estat actual dels terrenys, les condicions reals d'accés, les limitacions derivades de la coexistència amb les obres en curs i els condicionants que poden afectar la planificació i execució dels treballs.
+Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>350200.9</v>
+        <v>856364.91</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232150</t>
+          <t>45231110, 45232400, 45232410, 45232411</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=llLPwmCsTj4mMOlAXxDEjw%3D%3D</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300863221</t>
         </is>
       </c>
     </row>
@@ -3389,7 +2387,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -3403,22 +2401,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Aguas de Cádiz</t>
+          <t>EMASESA</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Renovación de infraestructura hidráulica en Calle General Luque</t>
+          <t>Proyecto de sustitución de las redes de abastecimiento, saneamiento e instalación de nueva red de baldeo de la Calle Vírgenes, por conservación. Distrito Casco Antiguo, Sevilla.</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>193779.79</v>
+        <v>707098.53</v>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3428,12 +2426,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>43328000, 45231300, 45232150, 45232400, 45232410</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RDQDicCcUYPi0Kd8%2Brcp6w%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=TkvLlQXSzqq2gkLQ8TeYKA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3444,7 +2442,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -3458,41 +2456,33 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ACOSOL</t>
+          <t>Empresa Municipal de Aguas de Gijón</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de "Redacción de proyectos, Dirección Facultativa y asistencia a la legalización de las instalaciones de protección contra incendios en diversas estaciones depuradoras de aguas residuales (EDARs) de ACOSOL"</t>
+          <t>Obras de reposición de las redes de abastecimiento y saneamiento afectadas por la rehabilitación de viviendas degradadas de la Obra Sindical de Contrueces (Fase I)</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>190000</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>350200.9</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71240000, 71520000</t>
+          <t>45231300, 45232150</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RXW343uwBxCkU02jNGj1Fw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=llLPwmCsTj4mMOlAXxDEjw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3517,22 +2507,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Consorcio de Aguas Bilbao Bizkaia</t>
+          <t>Aguas de Cádiz</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Obras de saneamiento en el barrio de Eleizondo en el término municipal de Zeanuri</t>
+          <t>Renovación de infraestructura hidráulica en Calle General Luque</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>275503.79</v>
+        <v>193779.79</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3542,12 +2532,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>43328000, 45231300, 45232150, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso616572/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RDQDicCcUYPi0Kd8%2Brcp6w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3558,7 +2548,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -3572,37 +2562,41 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MARE</t>
+          <t>ACOSOL</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Servicios de gestión de lodos de EDAR producidos en la Red de Saneamiento de Cantabria</t>
+          <t>Contratación del Servicio de "Redacción de proyectos, Dirección Facultativa y asistencia a la legalización de las instalaciones de protección contra incendios en diversas estaciones depuradoras de aguas residuales (EDARs) de ACOSOL"</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4089020.27</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+        <v>190000</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>90513700, 90513800</t>
+          <t>71000000, 71240000, 71520000</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DlbLIjNtKBaKeVWTb9Scog%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RXW343uwBxCkU02jNGj1Fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3613,7 +2607,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -3627,41 +2621,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+          <t>Consorcio de Aguas Bilbao Bizkaia</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Contratación del servicio de consultoría y asistencia técnica para la redacción del proyecto de ejecución, dirección de obra y coordinación de seguridad y salud de la reforma del campo de fútbol y pista de atletismo del estadio de Berazubi y nuevo edificio de gimnasios.</t>
+          <t>Obras de saneamiento en el barrio de Eleizondo en el término municipal de Zeanuri</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>96600</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>275503.79</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>71000000</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso736330/es_doc/index.html</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso616572/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -3672,7 +2662,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3686,41 +2676,37 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+          <t>MARE</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Contrato de servicios de redacción del proyecto básico y de ejecución, dirección facultativa de las obras y coordinación en materia de seguridad y salud de las obras de realización de una pista de atletismo de 200 metros en el municipio de Almussafes</t>
+          <t>Servicios de gestión de lodos de EDAR producidos en la Red de Saneamiento de Cantabria</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>39495.6</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>4089020.27</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71520000</t>
+          <t>90513700, 90513800</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XL%2BNTyDcCyWHCIsjvJ3rhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DlbLIjNtKBaKeVWTb9Scog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3731,7 +2717,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -3745,22 +2731,26 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MARE</t>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Drenaje de aguas procedentes de los desbordamientos de la acequia Mare y Barranco de Sotaia en suelo no urbanizable que entran en suelo urbanizable con ordenación pormenorizada Sector D</t>
+          <t>Contratación del servicio de consultoría y asistencia técnica para la redacción del proyecto de ejecución, dirección de obra y coordinación de seguridad y salud de la reforma del campo de fútbol y pista de atletismo del estadio de Berazubi y nuevo edificio de gimnasios.</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40377.8</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
+        <v>96600</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3770,12 +2760,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>71000000</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zo5cUizKxC5VYjgxA4nMUw%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso736330/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -3800,37 +2790,41 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación de tuberías de abastecimiento en urbanizaciones</t>
+          <t>Contrato de servicios de redacción del proyecto básico y de ejecución, dirección facultativa de las obras y coordinación en materia de seguridad y salud de las obras de realización de una pista de atletismo de 200 metros en el municipio de Almussafes</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2892150</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+        <v>39495.6</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45231110</t>
+          <t>71000000, 71520000</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-tuberias-abastecimiento-urbanizaciones</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XL%2BNTyDcCyWHCIsjvJ3rhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3855,37 +2849,37 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>MARE</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 67/2026 “Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P</t>
+          <t>Drenaje de aguas procedentes de los desbordamientos de la acequia Mare y Barranco de Sotaia en suelo no urbanizable que entran en suelo urbanizable con ordenación pormenorizada Sector D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2580718.9</v>
+        <v>40377.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311100</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato-0</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zo5cUizKxC5VYjgxA4nMUw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3896,7 +2890,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -3910,22 +2904,22 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>EMAYA</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>El objeto de este procedimiento es establecer las condiciones técnicas y económicas para el suministro de recambios eléctricos y mecánicos de los diferentes equipos que tiene instalados EMAYA en sus estaciones de impulsión.</t>
+          <t>Obras de renovación de tuberías de abastecimiento en urbanizaciones</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1074000</v>
+        <v>2892150</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3935,12 +2929,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31210000, 38420000, 42124200, 42996000</t>
+          <t>45231110</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XiV6iUa%2F7v4aF6cS8TCh%2FA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-tuberias-abastecimiento-urbanizaciones</t>
         </is>
       </c>
     </row>
@@ -3951,7 +2945,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -3965,41 +2959,37 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Metro de Madrid, S.A.</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Acuerdo marco para el suministro de mangas neumáticas destinadas al mantenimiento de los trenes del material móvil e instalaciones de Metro Madrid</t>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 67/2026 “Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>430000</v>
+        <v>2580718.9</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>44165000, 44165100, 44165300</t>
+          <t>71310000, 71311100</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/acuerdo-marco-suministro-mangas-neumaticas-destinadas-mantenimiento-trenes</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato-0</t>
         </is>
       </c>
     </row>
@@ -4010,7 +3000,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -4024,37 +3014,37 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMAYA</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de renovación de la red de saneamiento en el municipio de Santa María de la Alameda. Fase I (Plan Sanea 2500)” CYII 2026/25</t>
+          <t>El objeto de este procedimiento es establecer las condiciones técnicas y económicas para el suministro de recambios eléctricos y mecánicos de los diferentes equipos que tiene instalados EMAYA en sus estaciones de impulsión.</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>231900</v>
+        <v>1074000</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311000, 71311100, 71520000</t>
+          <t>31210000, 38420000, 42124200, 42996000</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/asistencia-tecnica-realizacion-trabajos-vigilancia-control-coordinacion-1</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XiV6iUa%2F7v4aF6cS8TCh%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4065,7 +3055,7 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -4079,37 +3069,41 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>Metro de Madrid, S.A.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Servicios de Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Chapinería. Fase I CYII 2026/15</t>
+          <t>Acuerdo marco para el suministro de mangas neumáticas destinadas al mantenimiento de los trenes del material móvil e instalaciones de Metro Madrid</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>231900</v>
+        <v>430000</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311000, 71311100, 71520000</t>
+          <t>44165000, 44165100, 44165300</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-realizacion-trabajos-vigilancia-control-0</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/acuerdo-marco-suministro-mangas-neumaticas-destinadas-mantenimiento-trenes</t>
         </is>
       </c>
     </row>
@@ -4139,32 +3133,32 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 53/2026 "Obras de renovación de tuberías de abastecimiento en urbanizaciones"</t>
+          <t>Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de renovación de la red de saneamiento en el municipio de Santa María de la Alameda. Fase I (Plan Sanea 2500)” CYII 2026/25</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>287158.38</v>
+        <v>231900</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311100</t>
+          <t>71310000, 71311000, 71311100, 71520000</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/asistencia-tecnica-realizacion-trabajos-vigilancia-control-coordinacion-1</t>
         </is>
       </c>
     </row>
@@ -4194,32 +3188,32 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación de la red de abastecimiento y saneamiento en la ciudad de Cáceres en las zonas: Barriada de San Blas, Calle Moreras, Camberos y Callejón de Trujillo</t>
+          <t>Servicios de Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Chapinería. Fase I CYII 2026/15</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>341928.01</v>
+        <v>231900</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45231110</t>
+          <t>71310000, 71311000, 71311100, 71520000</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-abastecimiento-saneamiento-ciudad-caceres-zonas-barriada-san</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-realizacion-trabajos-vigilancia-control-0</t>
         </is>
       </c>
     </row>
@@ -4230,7 +3224,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -4244,37 +3238,37 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Fortuna</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Concesión del servicio público de abastecimiento de agua potable y alcantarillado del municipio de Fortuna</t>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 53/2026 "Obras de renovación de tuberías de abastecimiento en urbanizaciones"</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>68949530.8</v>
+        <v>287158.38</v>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>65111000, 65130000, 90480000</t>
+          <t>71310000, 71311100</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RCFijR8b%2BYmcTfjQf3USOg%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato</t>
         </is>
       </c>
     </row>
@@ -4285,7 +3279,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -4299,37 +3293,37 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Pollença</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Contrato de servicios de mantenimiento y operación del servicio de alcantarillado del municipio de Pollença (Illes Balears)</t>
+          <t>Obras de renovación de la red de abastecimiento y saneamiento en la ciudad de Cáceres en las zonas: Barriada de San Blas, Calle Moreras, Camberos y Callejón de Trujillo</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2139325.94</v>
+        <v>341928.01</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>50510000, 90400000, 90470000, 90480000, 90491000</t>
+          <t>45231110</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=1e36YO6YJeHL1rX3q%2FMAPA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-abastecimiento-saneamiento-ciudad-caceres-zonas-barriada-san</t>
         </is>
       </c>
     </row>
@@ -4340,7 +3334,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -4354,37 +3348,37 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+          <t>Pleno del Ayuntamiento de Fortuna</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>La ejecución de las obras comprendidas en el proyecto de “OBRAS DE SANEAMIENTO EN LA ZONA COSTERA DE ARICO”, t.m. de Arico, redactado por la empresa CIVICA INGENIEROS, S.L, que contempla varias actuaciones en la red de saneamiento del municipio de Arico, seleccionadas de entre las medidas contenidas en el documento “Diagnóstico y Propuestas de Actuación en materia de Saneamiento".</t>
+          <t>Concesión del servicio público de abastecimiento de agua potable y alcantarillado del municipio de Fortuna</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1816937.94</v>
+        <v>68949530.8</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45233252</t>
+          <t>65111000, 65130000, 90480000</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DY9ZQkWH0O%2BLAncw3qdZkA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RCFijR8b%2BYmcTfjQf3USOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4395,7 +3389,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -4409,37 +3403,37 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+          <t>Pleno del Ayuntamiento de Benicàssim</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>"Red de Alcantarillado del ámbito de La Bastona", T.M.  de Santa Úrsula</t>
+          <t>Servicio de depuración, mantenimiento de la red de alcantarillado y emisario del Ayuntamiento de Benicàssim</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2057453.5</v>
+        <v>8149175.5</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232130, 45233252</t>
+          <t>90400000, 90480000, 90481000</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vQGQvWXwPLudkQsA7ROvsg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3uFezCRFv%2B3LIx6q1oPaMg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4464,41 +3458,37 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ayuntamiento de Cádiz</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Pollença</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Suministros necesarios para la celebración del Festival Manga de Cádiz FEMANCA 2026 (4 LOTES)</t>
+          <t>Contrato de servicios de mantenimiento y operación del servicio de alcantarillado del municipio de Pollença (Illes Balears)</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>58016</v>
+        <v>2139325.94</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>30236000, 31211100, 31527200, 32320000, 35111300</t>
+          <t>50510000, 90400000, 90470000, 90480000, 90491000</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3NalfqN%2FH1zzAq95uGTrDQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=1e36YO6YJeHL1rX3q%2FMAPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4509,7 +3499,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -4523,37 +3513,37 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+          <t>La ejecución de las obras comprendidas en el proyecto de “OBRAS DE SANEAMIENTO EN LA ZONA COSTERA DE ARICO”, t.m. de Arico, redactado por la empresa CIVICA INGENIEROS, S.L, que contempla varias actuaciones en la red de saneamiento del municipio de Arico, seleccionadas de entre las medidas contenidas en el documento “Diagnóstico y Propuestas de Actuación en materia de Saneamiento".</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>774510.76</v>
+        <v>1816937.94</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45231300, 45233252</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=V9R23eu82UwIYE3ZiZ%2BxmQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DY9ZQkWH0O%2BLAncw3qdZkA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4564,7 +3554,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
@@ -4578,37 +3568,37 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Puçol</t>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Obras 1ª fase del colector unitario de la C/Alicante en Puçol.</t>
+          <t>"Red de Alcantarillado del ámbito de La Bastona", T.M.  de Santa Úrsula</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>939454.59</v>
+        <v>2057453.5</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>45231300, 45232130, 45233252</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=WKz%2F6IjRhlfXOjazN1Dw9Q%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vQGQvWXwPLudkQsA7ROvsg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4619,7 +3609,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -4633,37 +3623,41 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Ajuntament de Sant Feliu de Guíxols</t>
+          <t>Junta de Gobierno del Ayuntamiento de Cádiz</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>El objeto del presente contrato es la prestación del servicio de mantenimiento, conservación, inspección y limpieza de la red de alcantarillado del término municipal de Sant Feliu de Guíxols. Dentro del servicio de mantenimiento se incluyen las tareas de inspección, limpieza y conservación de la red, así como la construcción de las acometidas de terceros a la mencionada red y el mantenimiento de las acometidas de los edificios de responsabilidad municipal, restante fuera de este contrato el mantenimiento de las redes de alcantarillado de cualquier otro organismo y de las acometidas de los edificios particulares.</t>
+          <t>Suministros necesarios para la celebración del Festival Manga de Cádiz FEMANCA 2026 (4 LOTES)</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1016373.82</v>
+        <v>58016</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>45232410, 90480000</t>
+          <t>30236000, 31211100, 31527200, 32320000, 35111300</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>https://contractaciopublica.cat/ca/detall-publicacio/6d8b7d9f-f3b1-48bc-889b-e6e04bacaf5e/300866915</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3NalfqN%2FH1zzAq95uGTrDQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4674,7 +3668,7 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
@@ -4688,22 +3682,22 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Consorcio Urbanístico Leganés Tecnológico</t>
+          <t>Consejo de Administración de Aigües i Sanejament d'Elx S.A.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>LGT_2026_CO_01 Proyecto constructivo e incoación del procedimiento de contratación de las obras de finalización del colector desdoblado del arroyo Butarque en el ámbito del PP-2, centro, del Plan de Sectorización Autovía Toledo Norte del Plan General de Ordenación Urbana de Leganés (MADRID), EXPEDIENTE CO/01/2026</t>
+          <t>Obras de la Red de Ejecución del Coletor de Peña Águilas y Llano de San José. Enlaces Fases 1-4 con Colector Primario</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>784673.0699999999</v>
+        <v>1539118.58</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4713,12 +3707,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/lgt2026co01-proyecto-constructivo-e-incoacion-procedimiento-contratacion-obras</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=n8WInzjdL2PLIx6q1oPaMg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4729,7 +3723,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -4743,37 +3737,37 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Narón</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Ampliacion da rede de saneamento en A Rocha (Sedes), comprendida no Plan provincial de cooperación ás obras e servizos de competencia municipal (Plan único de concellos) POS+Adicional 2/2025</t>
+          <t>Obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>384003.04</v>
+        <v>774510.76</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>44162500, 45232400, 45232410</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=GFxBe4DrBfvL1rX3q%2FMAPA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=V9R23eu82UwIYE3ZiZ%2BxmQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4784,7 +3778,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -4798,37 +3792,37 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Agüimes</t>
+          <t>Alcaldía del Ayuntamiento de Puçol</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Mejora y Optimización Red de Abastecimiento de Agua de Temisas</t>
+          <t>Obras 1ª fase del colector unitario de la C/Alicante en Puçol.</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>599625.8</v>
+        <v>939454.59</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45232400</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OxfluKxhWGV6nTs9LZ9RhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=WKz%2F6IjRhlfXOjazN1Dw9Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4839,7 +3833,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -4853,37 +3847,37 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Consejería de Industria, Energía, Ciencia y Territorio</t>
+          <t>Ajuntament de Sant Feliu de Guíxols</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>OBRAG26003 Nuevo colector en Rena (Badajoz)</t>
+          <t>El objeto del presente contrato es la prestación del servicio de mantenimiento, conservación, inspección y limpieza de la red de alcantarillado del término municipal de Sant Feliu de Guíxols. Dentro del servicio de mantenimiento se incluyen las tareas de inspección, limpieza y conservación de la red, así como la construcción de las acometidas de terceros a la mencionada red y el mantenimiento de las acometidas de los edificios de responsabilidad municipal, restante fuera de este contrato el mantenimiento de las redes de alcantarillado de cualquier otro organismo y de las acometidas de los edificios particulares.</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>395041.32</v>
+        <v>1016373.82</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232410, 90480000</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FgAgNDFSE7aKeVWTb9Scog%3D%3D</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/6d8b7d9f-f3b1-48bc-889b-e6e04bacaf5e/300866915</t>
         </is>
       </c>
     </row>
@@ -4894,7 +3888,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
@@ -4908,22 +3902,22 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de la Histórica Villa de los Realejos</t>
+          <t>Consorcio Urbanístico Leganés Tecnológico</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Contratación de obras del proyecto de "Remodelación del entorno urbano y adecuación de la red de abastecimiento en la urbanización Los Príncipes (Fase I)"</t>
+          <t>LGT_2026_CO_01 Proyecto constructivo e incoación del procedimiento de contratación de las obras de finalización del colector desdoblado del arroyo Butarque en el ámbito del PP-2, centro, del Plan de Sectorización Autovía Toledo Norte del Plan General de Ordenación Urbana de Leganés (MADRID), EXPEDIENTE CO/01/2026</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>517249.41</v>
+        <v>784673.0699999999</v>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4933,12 +3927,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45233222</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=VQOMAmLOSzeS81gZFETWmA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/lgt2026co01-proyecto-constructivo-e-incoacion-procedimiento-contratacion-obras</t>
         </is>
       </c>
     </row>
@@ -4963,37 +3957,37 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Administración de Limpieza y Mantenimiento de Carmona, S.L.U.</t>
+          <t>Alcaldía del Ayuntamiento de Narón</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Obras de rehabilitación de pavimentos y renovación de las redes de alcantarillado y abastecimiento de agua potable en la Barriada de Guadajoz. Fase 1</t>
+          <t>Ampliacion da rede de saneamento en A Rocha (Sedes), comprendida no Plan provincial de cooperación ás obras e servizos de competencia municipal (Plan único de concellos) POS+Adicional 2/2025</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>423938.36</v>
+        <v>384003.04</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>45232100, 45232150, 45232400, 45232410, 45233252</t>
+          <t>44162500, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bCgfi8hy24h9PLkba5eRog%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=GFxBe4DrBfvL1rX3q%2FMAPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5018,37 +4012,37 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Confederación Hidrográfica del Miño-Sil</t>
+          <t>Alcaldía del Ayuntamiento de Agüimes</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de colectores de la red de fecales de la calle Plácido Peña. T.M. de Vilalba (Lugo) PDM MIÑO-SIL ES010_2_ALCH0SBET29UR2023</t>
+          <t>Mejora y Optimización Red de Abastecimiento de Agua de Temisas</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>675986.95</v>
+        <v>599625.8</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=0sPmJ1%2FV1fD%2Fa9DgO%2BoYKQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OxfluKxhWGV6nTs9LZ9RhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5073,37 +4067,37 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Salamanca</t>
+          <t>Consejería de Industria, Energía, Ciencia y Territorio</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Obras de Renovación de la red de distribución de agua potable en varias calles de los barrios San Cristóbal, San Esteban y Fontana y en Pizarrales Norte.</t>
+          <t>OBRAG26003 Nuevo colector en Rena (Badajoz)</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>538921.6899999999</v>
+        <v>395041.32</v>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45233200</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Nzb4BMmgaFfIGlsa0Wad%2Bw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FgAgNDFSE7aKeVWTb9Scog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5128,37 +4122,37 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Cervo</t>
+          <t>Alcaldía del Ayuntamiento de la Histórica Villa de los Realejos</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Renovación beirarrúas e rede de saneamento da avenida da Mariña, en San Ciprián</t>
+          <t>Contratación de obras del proyecto de "Remodelación del entorno urbano y adecuación de la red de abastecimiento en la urbanización Los Príncipes (Fase I)"</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>458620.35</v>
+        <v>517249.41</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>45232410, 45233200, 45233252</t>
+          <t>45232150, 45233222</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hQUN1x2ScH%2BLAncw3qdZkA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=VQOMAmLOSzeS81gZFETWmA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5183,22 +4177,22 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Ibdes</t>
+          <t>Consejo de Administración de Limpieza y Mantenimiento de Carmona, S.L.U.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>El proyecto de "MEJORA DE SERVICIOS Y DE PAVIMENTOS" en Ibdes, tiene por objeto diversas obras de mejora de pavimentos y de las conducciones del alcantarillado y de distribución de agua en varios tramos de las Calles Rúa y Cerro de San Lorenzo.</t>
+          <t>Obras de rehabilitación de pavimentos y renovación de las redes de alcantarillado y abastecimiento de agua potable en la Barriada de Guadajoz. Fase 1</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>346698.53</v>
+        <v>423938.36</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5208,12 +4202,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45232400, 45233252</t>
+          <t>45232100, 45232150, 45232400, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HF9AC8k%2B%2F3mqb7rCcv76BA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bCgfi8hy24h9PLkba5eRog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5238,22 +4232,22 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+          <t>Presidencia de la Confederación Hidrográfica del Miño-Sil</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>La contratación de la ejecución de las obras de pavimentación y renovación de redes calle Agustina de Aragón números 58 a 76 y adyacentes (Fase 1) y calle Agustina de Aragón números 38 a 56 y calle La Huerta núm. 1 a 9 (Fase 2)</t>
+          <t>Proyecto de colectores de la red de fecales de la calle Plácido Peña. T.M. de Vilalba (Lugo) PDM MIÑO-SIL ES010_2_ALCH0SBET29UR2023</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>545400.61</v>
+        <v>675986.95</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5263,12 +4257,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>45231221, 45231300, 45233252</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OvOki5I9GBJrSd8H4b2soA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=0sPmJ1%2FV1fD%2Fa9DgO%2BoYKQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5293,37 +4287,37 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+          <t>Alcaldía del Ayuntamiento de Salamanca</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Las obras de pavimentación y renovación de redes</t>
+          <t>Obras de Renovación de la red de distribución de agua potable en varias calles de los barrios San Cristóbal, San Esteban y Fontana y en Pizarrales Norte.</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>545400</v>
+        <v>538921.6899999999</v>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>45231221, 45231300, 45233252</t>
+          <t>45231300, 45233200</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=38evUZBxaXWHCIsjvJ3rhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Nzb4BMmgaFfIGlsa0Wad%2Bw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5348,22 +4342,22 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Alcaldía del Ayuntamiento de Cervo</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+          <t>Renovación beirarrúas e rede de saneamento da avenida da Mariña, en San Ciprián</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>533872.4</v>
+        <v>458620.35</v>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5373,12 +4367,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>45232440, 45240000</t>
+          <t>45232410, 45233200, 45233252</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HnzMWLjwbK%2B8ebB%2FXTwy0A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hQUN1x2ScH%2BLAncw3qdZkA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5403,37 +4397,37 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>AGASA-Consejo de Administración</t>
+          <t>Alcaldía del Ayuntamiento de Ibdes</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Obras de instalación de la cuarta bomba de la EBAR Santa Catalina en la red de saneamiento de AGASA</t>
+          <t>El proyecto de "MEJORA DE SERVICIOS Y DE PAVIMENTOS" en Ibdes, tiene por objeto diversas obras de mejora de pavimentos y de las conducciones del alcantarillado y de distribución de agua en varios tramos de las Calles Rúa y Cerro de San Lorenzo.</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>465242.86</v>
+        <v>346698.53</v>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>45232152</t>
+          <t>45232150, 45232400, 45233252</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso733199/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HF9AC8k%2B%2F3mqb7rCcv76BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5458,22 +4452,22 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Artziniega-Pleno</t>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega (Fase 1)</t>
+          <t>La contratación de la ejecución de las obras de pavimentación y renovación de redes calle Agustina de Aragón números 58 a 76 y adyacentes (Fase 1) y calle Agustina de Aragón números 38 a 56 y calle La Huerta núm. 1 a 9 (Fase 2)</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>567293.62</v>
+        <v>545400.61</v>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5483,12 +4477,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45231221, 45231300, 45233252</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso31125/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OvOki5I9GBJrSd8H4b2soA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5513,37 +4507,37 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Basauri-Alcalde</t>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Obra de reposición del muro y la red de saneamiento en la trasera de la calle Luis Petralanda 1-3 de Basauri.</t>
+          <t>Las obras de pavimentación y renovación de redes</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>469741.46</v>
+        <v>545400</v>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231221, 45231300, 45233252</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso725833/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=38evUZBxaXWHCIsjvJ3rhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5554,7 +4548,7 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -5568,22 +4562,22 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Dirección Gerente de Aguas Vega Sierra Elvira, S.A.</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la red de abastecimiento de las calles Salitre, Vicente Aleixandre y Málaga, y la red de saneamiento de estas dos últimas, de Atarfe (Granada).</t>
+          <t>Ejecución de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>234044.63</v>
+        <v>533872.4</v>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5593,12 +4587,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>44160000, 45200000, 45220000, 45231100, 45232100</t>
+          <t>45232440, 45240000</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=cTWFE5D8Zh5VkTabT%2FRM8A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HnzMWLjwbK%2B8ebB%2FXTwy0A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5609,7 +4603,7 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -5623,37 +4617,37 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Carballo</t>
+          <t>AGASA-Consejo de Administración</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras: Red de abastecimiento de agua potable desde el lugar de Almacén al lugar de Vilar de Francos, en la parroquia de Artes (OBR 06/2026) incluída en el POS+Adicional 4/2025, 2ª Fase</t>
+          <t>Obras de instalación de la cuarta bomba de la EBAR Santa Catalina en la red de saneamiento de AGASA</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>247592.94</v>
+        <v>465242.86</v>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>45200000, 45231000, 45231300, 45232150</t>
+          <t>45232152</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=meSIPtE5fKQ7%2B9FIQYNjeQ%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso733199/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -5664,7 +4658,7 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -5678,37 +4672,37 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Aena. Dirección del Aeropuerto Adolfo Suárez Madrid-Barajas</t>
+          <t>Ayuntamiento de Artziniega-Pleno</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Proyecto Y Obra Acometida Red De Saneamiento Parcela Supermercado Aeroportuario</t>
+          <t>Renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega (Fase 1)</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>206300</v>
+        <v>567293.62</v>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=k1WCTiBaoektm4eBPtV6eQ%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso31125/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -5719,7 +4713,7 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
@@ -5733,37 +4727,37 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Autoridad Portuaria de la Bahía de Algeciras</t>
+          <t>Ayuntamiento de Basauri-Alcalde</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de desvio del ramal norte de la red de abastecimiento del área portuaria de Campamento</t>
+          <t>Obra de reposición del muro y la red de saneamiento en la trasera de la calle Luis Petralanda 1-3 de Basauri.</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>287137.15</v>
+        <v>469741.46</v>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232150</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=lc5tGIAbOAjmnwcj%2BxbdTg%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso725833/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -5788,37 +4782,37 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Hinojosa del Duque</t>
+          <t>Dirección Gerente de Aguas Vega Sierra Elvira, S.A.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Renovación del pavimento y red de saneamiento y agua potable de la Plaza Duque de Béjar de Hinojosa del Duque.</t>
+          <t>Renovación de la red de abastecimiento de las calles Salitre, Vicente Aleixandre y Málaga, y la red de saneamiento de estas dos últimas, de Atarfe (Granada).</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>314890.08</v>
+        <v>234044.63</v>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>45220000, 45232410, 45233251, 45233252</t>
+          <t>44160000, 45200000, 45220000, 45231100, 45232100</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=tomlDPx2VWQmMOlAXxDEjw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=cTWFE5D8Zh5VkTabT%2FRM8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5843,22 +4837,22 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Torralba de Ribota</t>
+          <t>Alcaldía del Ayuntamiento de Carballo</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Obras de pavimentado de calles y renovación de redes en el término municipal de TORRALBA DE RIBOTA</t>
+          <t>Contrato de obras: Red de abastecimiento de agua potable desde el lugar de Almacén al lugar de Vilar de Francos, en la parroquia de Artes (OBR 06/2026) incluída en el POS+Adicional 4/2025, 2ª Fase</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>192375.91</v>
+        <v>247592.94</v>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5868,12 +4862,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>45111100, 45232400, 45233252, 45330000</t>
+          <t>45200000, 45231000, 45231300, 45232150</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=H%2F59EKurpZ1SYrkJkLlFdw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=meSIPtE5fKQ7%2B9FIQYNjeQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5884,7 +4878,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -5898,37 +4892,37 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Cretas</t>
+          <t>Aena. Dirección del Aeropuerto Adolfo Suárez Madrid-Barajas</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de acondicionamiento y renovación de conducción de abastecimiento de agua</t>
+          <t>Proyecto Y Obra Acometida Red De Saneamiento Parcela Supermercado Aeroportuario</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>118205.83</v>
+        <v>206300</v>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FNDtn0ZSI8RxseVhcqrkhw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=k1WCTiBaoektm4eBPtV6eQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5939,7 +4933,7 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
@@ -5953,37 +4947,37 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Entidad Pública Empresarial Local Centros de Arte, Cultura y Turismo de Lanzarote</t>
+          <t>Presidencia de la Autoridad Portuaria de la Bahía de Algeciras</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Obra de nueva EBAR y tubería de impulsión en La Cueva de los Verdes</t>
+          <t>Proyecto de desvio del ramal norte de la red de abastecimiento del área portuaria de Campamento</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>102536.2</v>
+        <v>287137.15</v>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232411, 45232440</t>
+          <t>45231300, 45232150</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vwVlLdPv92qcCF8sV%2BqtYA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=lc5tGIAbOAjmnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5994,7 +4988,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -6008,37 +5002,37 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+          <t>Alcaldía del Ayuntamiento de Hinojosa del Duque</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Renovación de tubería de distribución en el vial público C/ Vicent Serra y actuaciones complementarias en el sistema de abastecimiento urbano de Sant Miquel de Balansat</t>
+          <t>Renovación del pavimento y red de saneamiento y agua potable de la Plaza Duque de Béjar de Hinojosa del Duque.</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>96500.2</v>
+        <v>314890.08</v>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+          <t>45220000, 45232410, 45233251, 45233252</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=c3vjWc0VQQ0aF6cS8TCh%2FA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=tomlDPx2VWQmMOlAXxDEjw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6049,7 +5043,7 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -6063,22 +5057,22 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+          <t>Pleno del Ayuntamiento de Torralba de Ribota</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Renovación de tubería de distribución en Plaza España y Calle Mossèn Vicent Ferrer i Guasch, con actuaciones complementarias en el sistema de abastecimiento urbano de Sant Joan de Labritja</t>
+          <t>Obras de pavimentado de calles y renovación de redes en el término municipal de TORRALBA DE RIBOTA</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>125890</v>
+        <v>192375.91</v>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6088,12 +5082,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+          <t>45111100, 45232400, 45233252, 45330000</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=2yr%2BUKjzV%2BGFlFRHfEzEaw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=H%2F59EKurpZ1SYrkJkLlFdw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6118,37 +5112,37 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Xunta de Goberno Local del Ayuntamiento de Boiro</t>
+          <t>Pleno del Ayuntamiento de Cretas</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Contratación para a execución da obra de Renovación de tramo de tubería de impulsión á estación de tratamento de auga potable (ETAP) de Boiro, mediante procedemento aberto e TRAMITACIÓN ANTICIPADA (DA 3.2 LCSP) vinculada subvención solicitada Augas de Galicia (DOG número 90 do 18 de maio de 2025) cofinanciada fondos FEDER programa 2021-2027(código proc. AU301E)</t>
+          <t>Proyecto de acondicionamiento y renovación de conducción de abastecimiento de agua</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>79632.66</v>
+        <v>118205.83</v>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=g3pTkEh1QTyS81gZFETWmA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FNDtn0ZSI8RxseVhcqrkhw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6173,37 +5167,37 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Cáceres</t>
+          <t>Entidad Pública Empresarial Local Centros de Arte, Cultura y Turismo de Lanzarote</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Renovación en la Red de Saneamiento de tramo en Calles Islas Baleares, Pedro Romero Mendoza y Arsenio Gallego, Recrecido de Pozos de Saneamiento en Parcela Municipal y Renovación de Acometida de Saneamiento del Camping Municipal de Cáceres.</t>
+          <t>Obra de nueva EBAR y tubería de impulsión en La Cueva de los Verdes</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>82975.21000000001</v>
+        <v>102536.2</v>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231300, 45232411, 45232440</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=nVZ97Q1pak%2FkY6rls5tG9A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vwVlLdPv92qcCF8sV%2BqtYA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6228,22 +5222,22 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Villablino</t>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obra de renovación de red de abastecimiento y aceras de la Calle Leitariegos en Villablino</t>
+          <t>Renovación de tubería de distribución en el vial público C/ Vicent Serra y actuaciones complementarias en el sistema de abastecimiento urbano de Sant Miquel de Balansat</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>147377.86</v>
+        <v>96500.2</v>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6253,12 +5247,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45233222</t>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2Fcvza%2BgevtBWhbmkna2nXQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=c3vjWc0VQQ0aF6cS8TCh%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6283,37 +5277,37 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Alginet</t>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la red de alcantarillado de la urbanización San Patricio d'Alginet (Fase I)</t>
+          <t>Renovación de tubería de distribución en Plaza España y Calle Mossèn Vicent Ferrer i Guasch, con actuaciones complementarias en el sistema de abastecimiento urbano de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>150364.75</v>
+        <v>125890</v>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>45200000, 45231300, 45232150, 45232400, 45232410</t>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=74A3N79XrwAeC9GJQOEBkQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=2yr%2BUKjzV%2BGFlFRHfEzEaw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6338,37 +5332,37 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Miengo</t>
+          <t>Xunta de Goberno Local del Ayuntamiento de Boiro</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la Red General de Abastecimiento en Avenida de Los Menicenses de Miengo en término municipal de Miengo</t>
+          <t>Contratación para a execución da obra de Renovación de tramo de tubería de impulsión á estación de tratamento de auga potable (ETAP) de Boiro, mediante procedemento aberto e TRAMITACIÓN ANTICIPADA (DA 3.2 LCSP) vinculada subvención solicitada Augas de Galicia (DOG número 90 do 18 de maio de 2025) cofinanciada fondos FEDER programa 2021-2027(código proc. AU301E)</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>80603.17</v>
+        <v>79632.66</v>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FfuggmFUPMKAAM7L03kM8A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=g3pTkEh1QTyS81gZFETWmA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6393,22 +5387,22 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Alcalà de Xivert</t>
+          <t>Alcaldía del Ayuntamiento de Cáceres</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Obras de mejoras hidráulicas en la red de saneamiento de Alcalà de Xivert-Alcossebre</t>
+          <t>Renovación en la Red de Saneamiento de tramo en Calles Islas Baleares, Pedro Romero Mendoza y Arsenio Gallego, Recrecido de Pozos de Saneamiento en Parcela Municipal y Renovación de Acometida de Saneamiento del Camping Municipal de Cáceres.</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>100541.82</v>
+        <v>82975.21000000001</v>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6423,7 +5417,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=a%2FsgtfkOGkAUqXM96WStVA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=nVZ97Q1pak%2FkY6rls5tG9A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6448,41 +5442,37 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Consejería Insular de Área de Cooperación Municipal y Vivienda del Cabildo Insular de Tenerife</t>
+          <t>Alcaldía del Ayuntamiento de Villablino</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>El objeto del contrato de servicios será la REDACCIÓN DEL PROYECTO y DIRECCIÓN DE LA OBRA denominada "REFORMA DE LA RED DE SANEAMIENTO DE LA CALETA DE INTERIÁN, FASE II", en el municipio de Garachico, incluidas en el Plan Insular de Cooperación a las obras y servicios de competencia municipal 2022-2026.</t>
+          <t>Contrato de obra de renovación de red de abastecimiento y aceras de la Calle Leitariegos en Villablino</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>99971.42</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>147377.86</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71240000</t>
+          <t>45232150, 45233222</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=P0CRmBEuH2%2Fmnwcj%2BxbdTg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2Fcvza%2BgevtBWhbmkna2nXQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6507,37 +5497,37 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Consell</t>
+          <t>Alcaldía del Ayuntamiento de Alginet</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras de renovación de la red de agua potable y mejora del firme del camino de Son Biel.</t>
+          <t>Renovación de la red de alcantarillado de la urbanización San Patricio d'Alginet (Fase I)</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>107187.43</v>
+        <v>150364.75</v>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>45232100, 45232150</t>
+          <t>45200000, 45231300, 45232150, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=ea7jddmClrhVq4S9zvaQpQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=74A3N79XrwAeC9GJQOEBkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6562,37 +5552,37 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Baena</t>
+          <t>Alcaldía del Ayuntamiento de Miengo</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Obras de mejora y ampliación de la red de saneamiento de la calle Matadero y confluencias de Avda Cañete de las Torres, calle Demetrio de los Ríos y calle Sargento Domingo Argudo.</t>
+          <t>Renovación de la Red General de Abastecimiento en Avenida de Los Menicenses de Miengo en término municipal de Miengo</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>69567.39999999999</v>
+        <v>80603.17</v>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>45112000, 45232400, 45232410</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=iNYtiIP2jyQeC9GJQOEBkQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FfuggmFUPMKAAM7L03kM8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6617,37 +5607,37 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Comisión ejecutiva del Consejo de Administración de la Empresa Municipal de Transportes de Fuenlabrada, S.A.</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Alcalà de Xivert</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Obras para la mejora integral de la red de saneamiento interior y construcción de un aseo auxiliar exterior en la campa de la EMTF</t>
+          <t>Obras de mejoras hidráulicas en la red de saneamiento de Alcalà de Xivert-Alcossebre</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>102721.88</v>
+        <v>100541.82</v>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>45215500, 45232400, 45232410, 45233252</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=eVV8%2BC8olRV4zIRvjBVCSw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=a%2FsgtfkOGkAUqXM96WStVA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6672,16 +5662,16 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Área de Fomento de la Diputación Provincial de Badajoz</t>
+          <t>Consejería Insular de Área de Cooperación Municipal y Vivienda del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la redacción del proyecto de ejecución, dirección de obras y coordinación de seguridad y salud, por lotes, para las obras de  mejora red de abastecimiento en varias localidades de la provincia de Badajoz. Cofinanciado al 85% por FEDER a través del Programa Plurirregional de España 2021-2027</t>
+          <t>El objeto del contrato de servicios será la REDACCIÓN DEL PROYECTO y DIRECCIÓN DE LA OBRA denominada "REFORMA DE LA RED DE SANEAMIENTO DE LA CALETA DE INTERIÁN, FASE II", en el municipio de Garachico, incluidas en el Plan Insular de Cooperación a las obras y servicios de competencia municipal 2022-2026.</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>112019.15</v>
+        <v>99971.42</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -6691,22 +5681,22 @@
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>71310000</t>
+          <t>71000000, 71240000</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=By3FKGFakezVGIpKDxgsAQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=P0CRmBEuH2%2Fmnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6731,37 +5721,37 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Alcaldia del Ayuntamiento de Argamasilla de Calatrava</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Consell</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Mejora de la red de abastecimiento de agua potable en el municipio de Argamasilla de Calatrava.</t>
+          <t>Contrato de obras de renovación de la red de agua potable y mejora del firme del camino de Son Biel.</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>88836.67999999999</v>
+        <v>107187.43</v>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45232100, 45232150</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=16Y%2BH5iLq9GP%2Bo96UAV7cQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=ea7jddmClrhVq4S9zvaQpQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6772,7 +5762,7 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
@@ -6786,22 +5776,22 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Valdemorales</t>
+          <t>Alcaldía del Ayuntamiento de Baena</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras correspondientes exclusivamente a la fase 1 conducción general del proyecto general de "modernización de la red de abastecimiento del municipio de  Valdemorales (Cáceres)</t>
+          <t>Obras de mejora y ampliación de la red de saneamiento de la calle Matadero y confluencias de Avda Cañete de las Torres, calle Demetrio de los Ríos y calle Sargento Domingo Argudo.</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>44037.27</v>
+        <v>69567.39999999999</v>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6811,12 +5801,12 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232150, 45233200, 45240000, 45252126</t>
+          <t>45112000, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=blNQxGZAd9JJ8Trn0ZPzLw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=iNYtiIP2jyQeC9GJQOEBkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6827,7 +5817,7 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
@@ -6841,22 +5831,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Comisión ejecutiva del Consejo de Administración de la Empresa Municipal de Transportes de Fuenlabrada, S.A.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Dirección de las obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+          <t>Obras para la mejora integral de la red de saneamiento interior y construcción de un aseo auxiliar exterior en la campa de la EMTF</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>61960.86</v>
+        <v>102721.88</v>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -6866,12 +5856,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>71300000, 71322000, 71520000</t>
+          <t>45215500, 45232400, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=MCV%2BAUHsDWnCfVQHDepjGQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=eVV8%2BC8olRV4zIRvjBVCSw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6882,7 +5872,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
@@ -6896,37 +5886,41 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Área de Fomento de la Diputación Provincial de Badajoz</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Dirección de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+          <t>Asistencia técnica para la redacción del proyecto de ejecución, dirección de obras y coordinación de seguridad y salud, por lotes, para las obras de  mejora red de abastecimiento en varias localidades de la provincia de Badajoz. Cofinanciado al 85% por FEDER a través del Programa Plurirregional de España 2021-2027</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44610.5</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
+        <v>112019.15</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>71300000, 71322000, 71520000</t>
+          <t>71310000</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=F%2FUx5m7rtlu8ebB%2FXTwy0A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=By3FKGFakezVGIpKDxgsAQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6937,7 +5931,7 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
@@ -6951,27 +5945,27 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de La Solana</t>
+          <t>Alcaldia del Ayuntamiento de Argamasilla de Calatrava</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Obras de Renovación de redes de abastecimiento en Calle Molinos de Viento, de La Solana (Ciudad Real)</t>
+          <t>Mejora de la red de abastecimiento de agua potable en el municipio de Argamasilla de Calatrava.</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>61709.77</v>
+        <v>88836.67999999999</v>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -6981,7 +5975,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hwqCatsJl8gS7pcxhTeWOg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=16Y%2BH5iLq9GP%2Bo96UAV7cQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6992,7 +5986,7 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
@@ -7006,37 +6000,37 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Ente Público Empresarial Augas de Galicia</t>
+          <t>Dirección Gerente de Aguas de Lorca, S.A.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>AUG-2026-0032: Obra de ampliación y mejora de la red de saneamiento integral del municipio. Saneamiento del Camino de la Torroeira. Parroquia de Louredo. Mos (Pontevedra). Actuación cofinanciada por la Unión Europea con el Fondo Europeo Agrícola de Desarrollo Rural (Feader) en un 60% del gasto elegible en el marco del Plan estratégico de la política agrícola común 2023_2027 (PEPAC) en Galicia.</t>
+          <t>Obras de renovación de redes municipales de abastecimiento de agua potable en el T.M. de Lorca</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>63904.44</v>
+        <v>117149.12</v>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231100, 45232100, 45232150, 45232151</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratosdegalicia.gal/licitacion?N=827669</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=7ek7iek2RL3%2Fa9DgO%2BoYKQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7047,7 +6041,7 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
@@ -7061,33 +6055,37 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Comisión Permanente de la Mancomunidad de Valdizarbe - Izarbeibarko Mankomunitatea</t>
+          <t>Alcaldía del Ayuntamiento de Canena</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación del colector de saneamiento de la Calle Santa María (campo de fútbol) en Obanos</t>
+          <t>Actuación de emergencia en la red de saneamiento en esquina calle Altozano y calle Iglesia, Canena (Jaén)</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>51496.63</v>
+        <v>82639.3</v>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>45112000, 45231300, 45232410, 45233252</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=8086&amp;Ticket=2608261225566A4631E8</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=yETWMHlcJJ0QyBAnWzHfCg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7112,37 +6110,37 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Mancomunidad de Mairaga</t>
+          <t>Alcaldía del Ayuntamiento de Valdemorales</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto y dirección facultativa de la obra de Pavimentación y renovación de redes de calles Barranco Salado, La Estanca y Bardenas Reales de Caparroso</t>
+          <t>Ejecución de las obras correspondientes exclusivamente a la fase 1 conducción general del proyecto general de "modernización de la red de abastecimiento del municipio de  Valdemorales (Cáceres)</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>43017.16</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>44037.27</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>71240000</t>
+          <t>45231300, 45232150, 45233200, 45240000, 45252126</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2608031429198E3AD3EC</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=blNQxGZAd9JJ8Trn0ZPzLw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7167,33 +6165,37 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Baztan</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>conexión a la red de saneamiento del barrio de Etxerri de Gartzain en el municipio de Baztan</t>
+          <t>Dirección de las obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>41206.09</v>
+        <v>61960.86</v>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>45231100, 45232150</t>
+          <t>71300000, 71322000, 71520000</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2607211228565F80EFF5</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=MCV%2BAUHsDWnCfVQHDepjGQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7218,26 +6220,22 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Portugalete -Alcalde</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la redacción del proyecto de renovación del colector H de la calle Miralrío de Portugalete.</t>
+          <t>Dirección de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>44610.5</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7247,12 +6245,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>71242000</t>
+          <t>71300000, 71322000, 71520000</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso702799/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=F%2FUx5m7rtlu8ebB%2FXTwy0A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -7263,7 +6261,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
@@ -7277,26 +6275,22 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Artziniega-Alcalde</t>
+          <t>Alcaldía del Ayuntamiento de La Solana</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Redacción del Proyecto y Dirección Facultativa para las obras de renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega- Fase II</t>
+          <t>Obras de Renovación de redes de abastecimiento en Calle Molinos de Viento, de La Solana (Ciudad Real)</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>19355</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>61709.77</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7306,23 +6300,23 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>71240000</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso398838/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hwqCatsJl8gS7pcxhTeWOg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
@@ -7336,103 +6330,99 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ACOSOL</t>
+          <t>Ente Público Empresarial Augas de Galicia</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Servicio de diseño, fabricación, suministro e instalación para la rehabilitación mediante manga de los colectores del saneamiento integral, tramo Marbella–Estepona (Lote 1)</t>
+          <t>AUG-2026-0032: Obra de ampliación y mejora de la red de saneamiento integral del municipio. Saneamiento del Camino de la Torroeira. Parroquia de Louredo. Mos (Pontevedra). Actuación cofinanciada por la Unión Europea con el Fondo Europeo Agrícola de Desarrollo Rural (Feader) en un 60% del gasto elegible en el marco del Plan estratégico de la política agrícola común 2023_2027 (PEPAC) en Galicia.</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>4030000</v>
+        <v>63904.44</v>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>90400000</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://www.contratosdegalicia.gal/licitacion?N=827669</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Águas e Energia do Porto</t>
+          <t>Comisión Permanente de la Mancomunidad de Valdizarbe - Izarbeibarko Mankomunitatea</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+          <t>Obras de renovación del colector de saneamiento de la Calle Santa María (campo de fútbol) en Obanos</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2100000</v>
+        <v>51496.63</v>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>sem vala</t>
-        </is>
-      </c>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>45112000, 45231300, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu/</t>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=8086&amp;Ticket=2608261225566A4631E8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
@@ -7446,16 +6436,16 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>AQUAVALL</t>
+          <t>Presidencia de la Mancomunidad de Mairaga</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+          <t>Redacción de proyecto y dirección facultativa de la obra de Pavimentación y renovación de redes de calles Barranco Salado, La Estanca y Bardenas Reales de Caparroso</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>180000</v>
+        <v>43017.16</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -7466,65 +6456,454 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>71322000</t>
+          <t>71240000</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2608031429198E3AD3EC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>SIMAS de Oeiras e Amadora</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Baztan</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+          <t>conexión a la red de saneamiento del barrio de Etxerri de Gartzain en el municipio de Baztan</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>890000</v>
+        <v>41206.09</v>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>45231100, 45232150</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2607211228565F80EFF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Portugalete -Alcalde</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Asistencia técnica para la redacción del proyecto de renovación del colector H de la calle Miralrío de Portugalete.</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>71242000</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso702799/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Presidencia de la Diputación Provincial de Palencia</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Renovación del Último Tramo de la Red de Saneamiento, Margen Izquierdo de la Calle Extramuros en San Cebrián de Campos</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>46232.23</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=8lAFGG5SIx9%2BF6L2uCfUWg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Artziniega-Alcalde</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Redacción del Proyecto y Dirección Facultativa para las obras de renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega- Fase II</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>19355</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>71240000</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso398838/es_doc/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Alcaldía del Ayuntamiento de Torre Pacheco</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Renovación de red de saneamiento y abastecimiento en el entorno e interior del Colegio Hernández Ardieta en Roldán.</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>33430.04</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Y9IK1q%2Bwcyz10HRJw8TEnQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>AQUAVALL</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>71322000</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Águas e Energia do Porto</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>sem vala</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>SIMAS de Oeiras e Amadora</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>890000</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
           <t>https://www.base.gov.pt/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M107"/>
+  <autoFilter ref="A1:M114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Radar_Detecciones.xlsx
+++ b/data/Radar_Detecciones.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6752,15 +6752,15 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>PLACSP</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6770,41 +6770,27 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>AQUAVALL</t>
+          <t>Ajuntament de Sant Feliu de Guíxols</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>España – Servicios de gestión de alcantarillados – Contrato para el servicio de mantenimiento, conservación y reposiciones o actuaciones de la red de alcantarillado y pluviales y elementos auxiliares dentro del término municipal de Sant Feliu de Guíxols</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>PUB</t>
-        </is>
-      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>71322000</t>
+          <t>90480000, 90480000</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://ted.europa.eu/es/notice/-/detail/593652-2026</t>
         </is>
       </c>
     </row>
@@ -6815,47 +6801,55 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Águas e Energia do Porto</t>
+          <t>AQUAVALL</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>sem vala</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
+        <v>180000</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>71322000</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu/</t>
+          <t>https://contrataciondelestado.es/</t>
         </is>
       </c>
     </row>
@@ -6866,11 +6860,11 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6880,30 +6874,81 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>SIMAS de Oeiras e Amadora</t>
+          <t>Águas e Energia do Porto</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>890000</v>
+        <v>2100000</v>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>sem vala</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
+          <t>https://ted.europa.eu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>SIMAS de Oeiras e Amadora</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>890000</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
           <t>https://www.base.gov.pt/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
+  <autoFilter ref="A1:M115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Radar_Detecciones.xlsx
+++ b/data/Radar_Detecciones.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Todas las detecciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -528,8 +528,173 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Obras del “Proyecto de Renovación de la Red de Saneamiento en el Municipio de Chapinería. Fase I (Plan Sanea 2500)”. CYII 2026/16</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4728984.64</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-renovacion-red-saneamiento-municipio-chapineria-fase-i-plan-sanea</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del Proyecto de Renovación de la Red de Saneamiento en el municipio de Corpa. Fase I (Plan Sanea 2500).”. CYII2026/30</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2276647.78</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-corpa-fase-i-plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Villar del Olmo. Fase I (Plan Sanea 2500)”. CYII 2025/25</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1341805.74</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45232410</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-villar-olmo-fase-i</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -540,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -628,11 +793,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -646,52 +811,48 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ACOSOL</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
+          <t>Obras del “Proyecto de Renovación de la Red de Saneamiento en el Municipio de Chapinería. Fase I (Plan Sanea 2500)”. CYII 2026/16</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>9990908.529999999</v>
+        <v>4728984.64</v>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>manga, manga continua</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-renovacion-red-saneamiento-municipio-chapineria-fase-i-plan-sanea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -705,52 +866,48 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ACOSOL</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>contratación por lotes del servicio de dirección facultativa de los trabajos de rehabilitación de colectores de la red de saneamiento integral de acosol, s.a. con manga cipp</t>
+          <t>Contrato de Obras del Proyecto de Renovación de la Red de Saneamiento en el municipio de Corpa. Fase I (Plan Sanea 2500).”. CYII2026/30</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>500991.77</v>
+        <v>2276647.78</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>cipp, manga</t>
-        </is>
-      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>44160000, 65000000, 71000000, 71500000, 71540000</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=259MiIPtVk7mnwcj%2BxbdTg%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-corpa-fase-i-plan</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -769,47 +926,43 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Villar del Olmo. Fase I (Plan Sanea 2500)”. CYII 2025/25</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>79450913.81</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>1341805.74</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45232420, 45232421</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-villar-olmo-fase-i</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -823,41 +976,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>EMATSA</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>L'objecte del present contracte son les obres de conservació i manteniment de col·lectors de la xarxa de clavegueram gestionada per EMATSA mitjançant instal·lació de mànega continua autoportant curada in situ (CIPP), d’acord amb les característiques i condicions fixades al plec de prescripcions tècniques regulador d’aquest contracte.</t>
+          <t>Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P.</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4401808.68</v>
+        <v>42450485.3</v>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>cipp, curada in situ</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45232151</t>
+          <t>45231110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://contractaciopublica.cat/ca/detall-publicacio/f39723ec-587b-4848-b53d-0180e5c0ff0d/300867025</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-adecuacion-galerias-red-abastecimiento-canal-isabel-ii-sa-mp</t>
         </is>
       </c>
     </row>
@@ -868,7 +1017,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -882,41 +1031,41 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>EMAYA</t>
+          <t>ACOSOL</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Servicio de redacción de proyecto básico de nueva IDAM (Instalación Desaladora de Agua de Mar) y tramitación administrativa de permisos vinculados para EMAYA</t>
+          <t>Contratación por lotes de los trabajos de diseño, fabricación, suministro e instalación de manga continua estructural para la rehabilitación de colectores de la red de saneamiento integral de Acosol, S.A</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>603300</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>9990908.529999999</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>manga, manga continua</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71311100, 71318000, 71322000</t>
+          <t>44160000, 44163000, 44163100, 44165000, 71000000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=qt5FN9id8YLIGlsa0Wad%2Bw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=u5Y%2FY5o%2FUeB%2FR5QFTlaM4A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -927,7 +1076,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -946,21 +1095,21 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de redacción del estudio de alternativas, estudios ambientales y anteproyecto de la remodelación de la E.D.A.R. Cerro del Águila (Fuengirola - Mijas) para ACOSOL, S.A.</t>
+          <t>contratación por lotes del servicio de dirección facultativa de los trabajos de rehabilitación de colectores de la red de saneamiento integral de acosol, s.a. con manga cipp</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>490348.91</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>500991.77</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>cipp, manga</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -970,12 +1119,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71243000, 71300000, 71311000, 71311300, 71322000</t>
+          <t>44160000, 65000000, 71000000, 71500000, 71540000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=EFuDWPmaJjQ2wEhQbcAqug%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=259MiIPtVk7mnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -986,7 +1135,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1000,37 +1149,41 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>EMALCSA</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Conservación, reparación y mantenimiento de las infraestructuras de agua y alcantarillado gestionadas por Emalcsa</t>
+          <t>Obras del proyecto de Construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del Tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4683636.14</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+        <v>79450913.81</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45112100, 45232150, 50000000, 65100000, 90400000</t>
+          <t>45232420, 45232421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=M48%2BHjPpqKeExvMJXBMHHQ%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-construccion-adecuacion-pnca-edar-poveda-redaccion-proyecto</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1194,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1055,22 +1208,26 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMATSA</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Santa María de la Alameda. Fase I (PLAN SANEA 2500)”. CYII 2026/24</t>
+          <t>L'objecte del present contracte son les obres de conservació i manteniment de col·lectors de la xarxa de clavegueram gestionada per EMATSA mitjançant instal·lació de mànega continua autoportant curada in situ (CIPP), d’acord amb les característiques i condicions fixades al plec de prescripcions tècniques regulador d’aquest contracte.</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5244670.28</v>
+        <v>4401808.68</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>cipp, curada in situ</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1080,12 +1237,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45232151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-santa-maria-alameda</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/f39723ec-587b-4848-b53d-0180e5c0ff0d/300867025</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1253,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1110,37 +1267,41 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMAYA</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Fresnedillas de la Oliva. Fase I (PLAN SANEA 2500)”. CYII 2026/11</t>
+          <t>Servicio de redacción de proyecto básico de nueva IDAM (Instalación Desaladora de Agua de Mar) y tramitación administrativa de permisos vinculados para EMAYA</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3310312.26</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+        <v>603300</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>71000000, 71311100, 71318000, 71322000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-fresnedillas-oliva</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=qt5FN9id8YLIGlsa0Wad%2Bw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1312,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1165,37 +1326,41 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>ACOSOL</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
+          <t>Servicio de redacción del estudio de alternativas, estudios ambientales y anteproyecto de la remodelación de la E.D.A.R. Cerro del Águila (Fuengirola - Mijas) para ACOSOL, S.A.</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1143886.29</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+        <v>490348.91</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>71243000, 71300000, 71311000, 71311300, 71322000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=EFuDWPmaJjQ2wEhQbcAqug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1371,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1220,37 +1385,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMALCSA</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Suministro de permanganato potásico para ETAP en la Delegación de Cáceres</t>
+          <t>Conservación, reparación y mantenimiento de las infraestructuras de agua y alcantarillado gestionadas por Emalcsa</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>26980</v>
+        <v>4683636.14</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24314100</t>
+          <t>45112100, 45232150, 50000000, 65100000, 90400000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/suministro-permanganato-potasico-etap-delegacion-caceres</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=M48%2BHjPpqKeExvMJXBMHHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1426,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1275,37 +1440,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Empresa Municipal de Aguas de Gijón</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación del colector de saneamiento en la Avenida Príncipe de Asturias, entre las calles Guatemala y Brasil (Gijón)</t>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Santa María de la Alameda. Fase I (PLAN SANEA 2500)”. CYII 2026/24</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>440676.07</v>
+        <v>5244670.28</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232400, 45232440</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=SnbVn%2Fo5sgGopEMYCmrbmw%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-santa-maria-alameda</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1481,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1330,37 +1495,37 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NILSA</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
+          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Fresnedillas de la Oliva. Fase I (PLAN SANEA 2500)”. CYII 2026/11</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>320078.64</v>
+        <v>3310312.26</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45233252</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-fresnedillas-oliva</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1536,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1385,33 +1550,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SCPSA — Servicios de la Comarca de Pamplona</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Colectores de pluviales en Pza. Valle de Aranguren de Mutilva (RM282370_01)</t>
+          <t>Contratacion de Obras del "Proyecto de Renovación de la Red de Saneamiento en el municipio de Ambite. FASE I (PLAN SANEA 2500)" CYII 2025/29</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>185937.04</v>
+        <v>1143886.29</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=3167&amp;Ticket=2608142133474FAF3BB0</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contratacion-obras-proyecto-renovacion-red-saneamiento-municipio-ambite-fase-i</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1591,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1436,37 +1605,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ACUAES</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras del "Proyecto actualizado del abastecimiento de agua a Jaca, TT.MM. de Villanúa, Castiello de Jaca y Jaca (Huesca)" y su "Adenda 06/24"</t>
+          <t>Suministro de permanganato potásico para ETAP en la Delegación de Cáceres</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6589764.84</v>
+        <v>26980</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45231100, 45231300, 45240000</t>
+          <t>24314100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Pp2GXUPs%2BC47u6%2B%2FR7DUoA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/suministro-permanganato-potasico-etap-delegacion-caceres</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1646,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1491,37 +1660,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>EMASESA</t>
+          <t>Empresa Municipal de Aguas de Gijón</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Proyecto para la renovación de las redes de abastecimiento y saneamiento en Avda. de la Reina Mercedes. Distrito Bellavista- La Palmera, Sevilla.</t>
+          <t>Obras de renovación del colector de saneamiento en la Avenida Príncipe de Asturias, entre las calles Guatemala y Brasil (Gijón)</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4408429.38</v>
+        <v>440676.07</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45231300, 45232400, 45232440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bJ7RafCEkY6cCF8sV%2BqtYA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=SnbVn%2Fo5sgGopEMYCmrbmw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1701,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1546,37 +1715,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EMACSA</t>
+          <t>NILSA</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Servicio para la ejecución de actuaciones integrales de mantenimiento, mejora y conservación de infraestructuras del ciclo integral del agua gestionadas por EMACSA.</t>
+          <t>Zalain industrialdeko gainerako industriak Nilsaren hustubidearekin lotu proiektuko 2. fasearen obrak/Obras de la fase 2 del proyecto de Conexión del resto de industrias del polígono de Zalain al emisario en vacío de Nilsa</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>32094518.03</v>
+        <v>320078.64</v>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45232151, 50532000, 50800000, 90400000</t>
+          <t>45231300, 45233252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zZBMviMwMpEeC9GJQOEBkQ%3D%3D</t>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=260813090028FD602D46</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1756,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1601,41 +1770,33 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>SCPSA — Servicios de la Comarca de Pamplona</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Servicios de asistencia técnica y coordinación de seguridad y salud para la supervisión y control del desarrollo de las obras del “proyecto de construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)”</t>
+          <t>Colectores de pluviales en Pza. Valle de Aranguren de Mutilva (RM282370_01)</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>350174459</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>185937.04</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311100</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-coordinacion-seguridad-salud-supervision-control-27</t>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=3167&amp;Ticket=2608142133474FAF3BB0</t>
         </is>
       </c>
     </row>
@@ -1660,26 +1821,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>ACUAES</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Servicios de asistencia técnica para la redacción de proyectos y pliegos de estaciones de tratamiento de agua (Potable, Residual y Regenerada)</t>
+          <t>Ejecución de las obras del "Proyecto actualizado del abastecimiento de agua a Jaca, TT.MM. de Villanúa, Castiello de Jaca y Jaca (Huesca)" y su "Adenda 06/24"</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>6589764.84</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1689,12 +1846,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71242000, 71300000, 71311000, 71330000</t>
+          <t>45231100, 45231300, 45240000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-pliegos-estaciones-tratamiento-1</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Pp2GXUPs%2BC47u6%2B%2FR7DUoA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1719,37 +1876,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMASESA</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Obras de mejora de Redes de Saneamiento gestionadas por Canal de Isabel II, S.A., M.P. – PLAN SANEA 2</t>
+          <t>Proyecto para la renovación de las redes de abastecimiento y saneamiento en Avda. de la Reina Mercedes. Distrito Bellavista- La Palmera, Sevilla.</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>214220312.18</v>
+        <v>4408429.38</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-mejora-redes-saneamiento-gestionadas-canal-isabel-ii-sa-mp-plan-sanea-2</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bJ7RafCEkY6cCF8sV%2BqtYA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1774,41 +1931,37 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMACSA</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Servicios de asistencia técnica para la redacción de proyectos de infraestructuras hidráulicas y aprovechamientos energéticos</t>
+          <t>Servicio para la ejecución de actuaciones integrales de mantenimiento, mejora y conservación de infraestructuras del ciclo integral del agua gestionadas por EMACSA.</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>32094518.03</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71242000, 71300000, 71311000, 71330000</t>
+          <t>45232150, 45232151, 50532000, 50800000, 90400000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-infraestructuras-hidraulicas-0</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zZBMviMwMpEeC9GJQOEBkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1838,32 +1991,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Servicios de conservación y mantenimiento de las redes de saneamiento periférico gestionadas por Canal de Isabel II, S.A., M.P.</t>
+          <t>Servicios de asistencia técnica y coordinación de seguridad y salud para la supervisión y control del desarrollo de las obras del “proyecto de construcción para la adecuación al PNCA de la EDAR de la Poveda y redacción del proyecto y ejecución de las obras del tratamiento cuaternario de la EDAR la Poveda (T.M. Arganda del Rey)”</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>285736930.5</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+        <v>350174459</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50000000, 90400000</t>
+          <t>71310000, 71311100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-conservacion-mantenimiento-redes-saneamiento-periferico-gestionadas</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-coordinacion-seguridad-salud-supervision-control-27</t>
         </is>
       </c>
     </row>
@@ -1874,7 +2031,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1888,22 +2045,26 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>AGUASVIRA</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Servicio de limpieza de la red e instalaciones de saneamiento gestionadas por la empresa Aguasvira</t>
+          <t>Servicios de asistencia técnica para la redacción de proyectos y pliegos de estaciones de tratamiento de agua (Potable, Residual y Regenerada)</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1897500</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+        <v>8000000</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1913,12 +2074,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90400000, 90470000, 90513600, 90513700</t>
+          <t>71242000, 71300000, 71311000, 71330000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2F9%2BLOFDQWW7N3k3tjedSGw%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-pliegos-estaciones-tratamiento-1</t>
         </is>
       </c>
     </row>
@@ -1929,7 +2090,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1943,37 +2104,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ACUAES</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras del Proyecto "Obras y actuaciones para la mejora de las instalaciones del sistema de abastecimiento del Valle Esgueva (Valladolid)".</t>
+          <t>Obras de mejora de Redes de Saneamiento gestionadas por Canal de Isabel II, S.A., M.P. – PLAN SANEA 2</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2187973.19</v>
+        <v>214220312.18</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45213260, 45232150, 45252126</t>
+          <t>45232400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HOwdh03hNTSOUi78BmzhOQ%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-mejora-redes-saneamiento-gestionadas-canal-isabel-ii-sa-mp-plan-sanea-2</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2145,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1998,37 +2159,41 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ESAMUR</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Estación depuradora de aguas residuales de Cañadas de San Pedro (Murcia)</t>
+          <t>Servicios de asistencia técnica para la redacción de proyectos de infraestructuras hidráulicas y aprovechamientos energéticos</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2395990.69</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+        <v>10500000</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45232420, 45232430</t>
+          <t>71242000, 71300000, 71311000, 71330000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=56qhfPOd%2Fw%2FIGlsa0Wad%2Bw%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-proyectos-infraestructuras-hidraulicas-0</t>
         </is>
       </c>
     </row>
@@ -2039,136 +2204,356 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Canal de Isabel II</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de conservación y mantenimiento de las redes de saneamiento periférico gestionadas por Canal de Isabel II, S.A., M.P.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>285736930.5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>50000000, 90400000</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-conservacion-mantenimiento-redes-saneamiento-periferico-gestionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>AGUASVIRA</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de limpieza de la red e instalaciones de saneamiento gestionadas por la empresa Aguasvira</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1897500</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>90400000, 90470000, 90513600, 90513700</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2F9%2BLOFDQWW7N3k3tjedSGw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>ACUAES</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Ejecución de las obras del Proyecto "Obras y actuaciones para la mejora de las instalaciones del sistema de abastecimiento del Valle Esgueva (Valladolid)".</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>2187973.19</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>45213260, 45232150, 45252126</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HOwdh03hNTSOUi78BmzhOQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>ESAMUR</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Estación depuradora de aguas residuales de Cañadas de San Pedro (Murcia)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2395990.69</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>45232420, 45232430</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=56qhfPOd%2Fw%2FIGlsa0Wad%2Bw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>L’objecte del present contracte és l’execució de les obres de manteniment i reparació per a corregir i millorar les condicions d’explotació d’alguns dipòsits de la Zona sud d’ATL, elegits segons la rellevància dels esmentats informes, a excepció d’aquells dipòsits on a l’actualitat s’hi estan duen a terme o hi ha previst actuacions especifiques de renovació o manteniment, o bé que per diferents circumstancies el termini d’execució dels treballs es superior al temps que el dipòsit en qüestió pot estar sense prestar el servei.
 Els dipòsit a rehabilitar estan situats al termes municipals de: Òdena, Moja, Avinyonet del Penedès, Piera, Sant Esteve Sesrovires, Masquefa, Sant Andreu de la Barca, Castellbisbal, Pallejà, Rubí, Sabadell, Sant Quirze del Vallès i Castellar del Vallès.
 Els treballs a realitzar són específics per a cada dipòsit i estan descrits detalladament al projecte constructiu corresponent.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G31" s="3" t="n">
         <v>3161756.55</v>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>RES</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>45232150</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>https://contractaciopublica.cat/ca/detall-publicacio/2cd3edde-16d5-4278-931d-968d40ffb17f/300859539</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>EMAYA</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Renovación red de agua potable y saneamiento en zona C/Saridakis</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>992163.92</v>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>RES</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>45232150, 45232410</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Q%2B3PBn4BGMdVq4S9zvaQpQ%3D%3D</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Aigües de Manresa</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
 La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
@@ -2177,116 +2562,116 @@
 Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>856364.91</v>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>2027-01-29</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>45231110, 45232400, 45232410, 45232411</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300862918</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Canal de Isabel II</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Servicios de asistencia técnica para la redacción de documentos normativos, proyectos en las instalaciones de las presas de Canal de Isabel II, S.A. M.P. y estudios técnicos de cantidad y calidad del recurso en los embalses y masas de agua de la Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G34" s="3" t="n">
         <v>1440000</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>RES</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>71311000</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-redaccion-documentos-normativos-proyectos</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Aigües de Manresa</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
 La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
@@ -2295,57 +2680,57 @@
 Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G35" s="3" t="n">
         <v>856364.91</v>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>2027-01-29</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>ADJ</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>45231110, 45232400, 45232410, 45232411</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300863597</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Aigües de Manresa</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Execució de les obres corresponents al Projecte pel sanejament del municipi de Súria mitjançant la connexió al sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada (Fase 4), consistents en la construcció d'un col·lector en alta mitjançant una canonada de polietilè DN315 que permetrà la connexió del sistema de sanejament de Súria amb el sistema de l'Estació Depuradora d'Aigües Residuals de Manresa-Sant Joan de Vilatorrada. 
 La visita prèvia als terrenys objecte de les obres tindrà caràcter obligatori.
@@ -2354,249 +2739,29 @@
 Aquesta necessitat esdevé especialment rellevant atès que la coordinació de les obres concurrents constitueix un element essencial de l'execució del contracte i un aspecte directament vinculat als criteris d'adjudicació i a les obligacions contractuals que haurà d'assumir l'adjudicatari. (Informació sobre la visita consultar clàusula 4 del PCP i Tauler d'avisos en aquest expedient)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G36" s="3" t="n">
         <v>856364.91</v>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2027-01-29</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EV</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>45231110, 45232400, 45232410, 45232411</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300863221</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>EMASESA</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto de sustitución de las redes de abastecimiento, saneamiento e instalación de nueva red de baldeo de la Calle Vírgenes, por conservación. Distrito Casco Antiguo, Sevilla.</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>707098.53</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>ADJ</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>45231300</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=TkvLlQXSzqq2gkLQ8TeYKA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Empresa Municipal de Aguas de Gijón</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Obras de reposición de las redes de abastecimiento y saneamiento afectadas por la rehabilitación de viviendas degradadas de la Obra Sindical de Contrueces (Fase I)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>350200.9</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>45231300, 45232150</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=llLPwmCsTj4mMOlAXxDEjw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Aguas de Cádiz</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Renovación de infraestructura hidráulica en Calle General Luque</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>193779.79</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>ADJ</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>43328000, 45231300, 45232150, 45232400, 45232410</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RDQDicCcUYPi0Kd8%2Brcp6w%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>ACOSOL</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Contratación del Servicio de "Redacción de proyectos, Dirección Facultativa y asistencia a la legalización de las instalaciones de protección contra incendios en diversas estaciones depuradoras de aguas residuales (EDARs) de ACOSOL"</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>190000</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71240000, 71520000</t>
+          <t>45231110, 45232400, 45232410, 45232411</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RXW343uwBxCkU02jNGj1Fw%3D%3D</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/423dfe77-d0cf-4b99-94e6-6c40bd349878/300863221</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2772,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -2621,22 +2786,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Consorcio de Aguas Bilbao Bizkaia</t>
+          <t>EMASESA</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Obras de saneamiento en el barrio de Eleizondo en el término municipal de Zeanuri</t>
+          <t>Proyecto de sustitución de las redes de abastecimiento, saneamiento e instalación de nueva red de baldeo de la Calle Vírgenes, por conservación. Distrito Casco Antiguo, Sevilla.</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>275503.79</v>
+        <v>707098.53</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2651,7 +2816,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso616572/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=TkvLlQXSzqq2gkLQ8TeYKA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2827,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -2676,37 +2841,33 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MARE</t>
+          <t>Empresa Municipal de Aguas de Gijón</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Servicios de gestión de lodos de EDAR producidos en la Red de Saneamiento de Cantabria</t>
+          <t>Obras de reposición de las redes de abastecimiento y saneamiento afectadas por la rehabilitación de viviendas degradadas de la Obra Sindical de Contrueces (Fase I)</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>4089020.27</v>
+        <v>350200.9</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>90513700, 90513800</t>
+          <t>45231300, 45232150</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DlbLIjNtKBaKeVWTb9Scog%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=llLPwmCsTj4mMOlAXxDEjw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2878,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -2731,41 +2892,37 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+          <t>Aguas de Cádiz</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Contratación del servicio de consultoría y asistencia técnica para la redacción del proyecto de ejecución, dirección de obra y coordinación de seguridad y salud de la reforma del campo de fútbol y pista de atletismo del estadio de Berazubi y nuevo edificio de gimnasios.</t>
+          <t>Renovación de infraestructura hidráulica en Calle General Luque</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>96600</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>193779.79</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>71000000</t>
+          <t>43328000, 45231300, 45232150, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso736330/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RDQDicCcUYPi0Kd8%2Brcp6w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2933,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -2790,16 +2947,16 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
+          <t>ACOSOL</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Contrato de servicios de redacción del proyecto básico y de ejecución, dirección facultativa de las obras y coordinación en materia de seguridad y salud de las obras de realización de una pista de atletismo de 200 metros en el municipio de Almussafes</t>
+          <t>Contratación del Servicio de "Redacción de proyectos, Dirección Facultativa y asistencia a la legalización de las instalaciones de protección contra incendios en diversas estaciones depuradoras de aguas residuales (EDARs) de ACOSOL"</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>39495.6</v>
+        <v>190000</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2809,22 +2966,22 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71520000</t>
+          <t>71000000, 71240000, 71520000</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XL%2BNTyDcCyWHCIsjvJ3rhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RXW343uwBxCkU02jNGj1Fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2992,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -2849,37 +3006,37 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MARE</t>
+          <t>Consorcio de Aguas Bilbao Bizkaia</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Drenaje de aguas procedentes de los desbordamientos de la acequia Mare y Barranco de Sotaia en suelo no urbanizable que entran en suelo urbanizable con ordenación pormenorizada Sector D</t>
+          <t>Obras de saneamiento en el barrio de Eleizondo en el término municipal de Zeanuri</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>40377.8</v>
+        <v>275503.79</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zo5cUizKxC5VYjgxA4nMUw%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso616572/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -2890,7 +3047,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -2904,37 +3061,37 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>MARE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación de tuberías de abastecimiento en urbanizaciones</t>
+          <t>Servicios de gestión de lodos de EDAR producidos en la Red de Saneamiento de Cantabria</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2892150</v>
+        <v>4089020.27</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45231110</t>
+          <t>90513700, 90513800</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-tuberias-abastecimiento-urbanizaciones</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DlbLIjNtKBaKeVWTb9Scog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3102,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -2959,37 +3116,41 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 67/2026 “Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P</t>
+          <t>Contratación del servicio de consultoría y asistencia técnica para la redacción del proyecto de ejecución, dirección de obra y coordinación de seguridad y salud de la reforma del campo de fútbol y pista de atletismo del estadio de Berazubi y nuevo edificio de gimnasios.</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2580718.9</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+        <v>96600</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311100</t>
+          <t>71000000</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato-0</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso736330/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3161,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -3014,37 +3175,41 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>EMAYA</t>
+          <t>ATL — Ens d'Abastament d'Aigua Ter-Llobregat</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>El objeto de este procedimiento es establecer las condiciones técnicas y económicas para el suministro de recambios eléctricos y mecánicos de los diferentes equipos que tiene instalados EMAYA en sus estaciones de impulsión.</t>
+          <t>Contrato de servicios de redacción del proyecto básico y de ejecución, dirección facultativa de las obras y coordinación en materia de seguridad y salud de las obras de realización de una pista de atletismo de 200 metros en el municipio de Almussafes</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1074000</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+        <v>39495.6</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>31210000, 38420000, 42124200, 42996000</t>
+          <t>71000000, 71520000</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XiV6iUa%2F7v4aF6cS8TCh%2FA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XL%2BNTyDcCyWHCIsjvJ3rhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3220,7 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -3069,41 +3234,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Metro de Madrid, S.A.</t>
+          <t>MARE</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Acuerdo marco para el suministro de mangas neumáticas destinadas al mantenimiento de los trenes del material móvil e instalaciones de Metro Madrid</t>
+          <t>Drenaje de aguas procedentes de los desbordamientos de la acequia Mare y Barranco de Sotaia en suelo no urbanizable que entran en suelo urbanizable con ordenación pormenorizada Sector D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>430000</v>
+        <v>40377.8</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>44165000, 44165100, 44165300</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/acuerdo-marco-suministro-mangas-neumaticas-destinadas-mantenimiento-trenes</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=zo5cUizKxC5VYjgxA4nMUw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3275,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -3133,32 +3294,32 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de renovación de la red de saneamiento en el municipio de Santa María de la Alameda. Fase I (Plan Sanea 2500)” CYII 2026/25</t>
+          <t>Obras de renovación de tuberías de abastecimiento en urbanizaciones</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>231900</v>
+        <v>2892150</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311000, 71311100, 71520000</t>
+          <t>45231110</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/asistencia-tecnica-realizacion-trabajos-vigilancia-control-coordinacion-1</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-tuberias-abastecimiento-urbanizaciones</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3330,7 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
@@ -3188,32 +3349,32 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Servicios de Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Chapinería. Fase I CYII 2026/15</t>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 67/2026 “Obras de renovación de red y adecuación de galerías de la red de abastecimiento de Canal de Isabel II, S.A., M.P</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>231900</v>
+        <v>2580718.9</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311000, 71311100, 71520000</t>
+          <t>71310000, 71311100</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-realizacion-trabajos-vigilancia-control-0</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato-0</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3385,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -3238,22 +3399,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>EMAYA</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 53/2026 "Obras de renovación de tuberías de abastecimiento en urbanizaciones"</t>
+          <t>El objeto de este procedimiento es establecer las condiciones técnicas y económicas para el suministro de recambios eléctricos y mecánicos de los diferentes equipos que tiene instalados EMAYA en sus estaciones de impulsión.</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>287158.38</v>
+        <v>1074000</v>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3263,12 +3424,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>71310000, 71311100</t>
+          <t>31210000, 38420000, 42124200, 42996000</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=XiV6iUa%2F7v4aF6cS8TCh%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3440,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -3293,37 +3454,41 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Canal de Isabel II</t>
+          <t>Metro de Madrid, S.A.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación de la red de abastecimiento y saneamiento en la ciudad de Cáceres en las zonas: Barriada de San Blas, Calle Moreras, Camberos y Callejón de Trujillo</t>
+          <t>Acuerdo marco para el suministro de mangas neumáticas destinadas al mantenimiento de los trenes del material móvil e instalaciones de Metro Madrid</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>341928.01</v>
+        <v>430000</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>45231110</t>
+          <t>44165000, 44165100, 44165300</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-abastecimiento-saneamiento-ciudad-caceres-zonas-barriada-san</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/acuerdo-marco-suministro-mangas-neumaticas-destinadas-mantenimiento-trenes</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3499,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -3348,37 +3513,37 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Fortuna</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Concesión del servicio público de abastecimiento de agua potable y alcantarillado del municipio de Fortuna</t>
+          <t>Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de renovación de la red de saneamiento en el municipio de Santa María de la Alameda. Fase I (Plan Sanea 2500)” CYII 2026/25</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>68949530.8</v>
+        <v>231900</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>65111000, 65130000, 90480000</t>
+          <t>71310000, 71311000, 71311100, 71520000</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RCFijR8b%2BYmcTfjQf3USOg%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/asistencia-tecnica-realizacion-trabajos-vigilancia-control-coordinacion-1</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3554,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -3403,22 +3568,22 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Benicàssim</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Servicio de depuración, mantenimiento de la red de alcantarillado y emisario del Ayuntamiento de Benicàssim</t>
+          <t>Servicios de Asistencia Técnica para la realización de los trabajos de vigilancia, control y de coordinación de seguridad y salud, durante la ejecución de las obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Chapinería. Fase I CYII 2026/15</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>8149175.5</v>
+        <v>231900</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3428,12 +3593,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>90400000, 90480000, 90481000</t>
+          <t>71310000, 71311000, 71311100, 71520000</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3uFezCRFv%2B3LIx6q1oPaMg%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-asistencia-tecnica-realizacion-trabajos-vigilancia-control-0</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3609,7 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -3458,22 +3623,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Pollença</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Contrato de servicios de mantenimiento y operación del servicio de alcantarillado del municipio de Pollença (Illes Balears)</t>
+          <t>Servicios de dirección de obras y coordinación de seguridad y salud de las obras a ejecutar en el contrato 53/2026 "Obras de renovación de tuberías de abastecimiento en urbanizaciones"</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2139325.94</v>
+        <v>287158.38</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3483,12 +3648,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>50510000, 90400000, 90470000, 90480000, 90491000</t>
+          <t>71310000, 71311100</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=1e36YO6YJeHL1rX3q%2FMAPA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/servicios-direccion-obras-coordinacion-seguridad-salud-obras-ejecutar-contrato</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3664,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -3513,37 +3678,37 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+          <t>Canal de Isabel II</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>La ejecución de las obras comprendidas en el proyecto de “OBRAS DE SANEAMIENTO EN LA ZONA COSTERA DE ARICO”, t.m. de Arico, redactado por la empresa CIVICA INGENIEROS, S.L, que contempla varias actuaciones en la red de saneamiento del municipio de Arico, seleccionadas de entre las medidas contenidas en el documento “Diagnóstico y Propuestas de Actuación en materia de Saneamiento".</t>
+          <t>Obras de renovación de la red de abastecimiento y saneamiento en la ciudad de Cáceres en las zonas: Barriada de San Blas, Calle Moreras, Camberos y Callejón de Trujillo</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1816937.94</v>
+        <v>341928.01</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45233252</t>
+          <t>45231110</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DY9ZQkWH0O%2BLAncw3qdZkA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-renovacion-red-abastecimiento-saneamiento-ciudad-caceres-zonas-barriada-san</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3719,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
@@ -3568,37 +3733,37 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
+          <t>Pleno del Ayuntamiento de Fortuna</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>"Red de Alcantarillado del ámbito de La Bastona", T.M.  de Santa Úrsula</t>
+          <t>Concesión del servicio público de abastecimiento de agua potable y alcantarillado del municipio de Fortuna</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2057453.5</v>
+        <v>68949530.8</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232130, 45233252</t>
+          <t>65111000, 65130000, 90480000</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vQGQvWXwPLudkQsA7ROvsg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=RCFijR8b%2BYmcTfjQf3USOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3774,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -3623,41 +3788,37 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ayuntamiento de Cádiz</t>
+          <t>Pleno del Ayuntamiento de Benicàssim</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Suministros necesarios para la celebración del Festival Manga de Cádiz FEMANCA 2026 (4 LOTES)</t>
+          <t>Servicio de depuración, mantenimiento de la red de alcantarillado y emisario del Ayuntamiento de Benicàssim</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>58016</v>
+        <v>8149175.5</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>manga</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>30236000, 31211100, 31527200, 32320000, 35111300</t>
+          <t>90400000, 90480000, 90481000</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3NalfqN%2FH1zzAq95uGTrDQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3uFezCRFv%2B3LIx6q1oPaMg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3682,22 +3843,22 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Administración de Aigües i Sanejament d'Elx S.A.</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Pollença</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Obras de la Red de Ejecución del Coletor de Peña Águilas y Llano de San José. Enlaces Fases 1-4 con Colector Primario</t>
+          <t>Contrato de servicios de mantenimiento y operación del servicio de alcantarillado del municipio de Pollença (Illes Balears)</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1539118.58</v>
+        <v>2139325.94</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3707,12 +3868,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>50510000, 90400000, 90470000, 90480000, 90491000</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=n8WInzjdL2PLIx6q1oPaMg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=1e36YO6YJeHL1rX3q%2FMAPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3884,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -3737,37 +3898,37 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+          <t>La ejecución de las obras comprendidas en el proyecto de “OBRAS DE SANEAMIENTO EN LA ZONA COSTERA DE ARICO”, t.m. de Arico, redactado por la empresa CIVICA INGENIEROS, S.L, que contempla varias actuaciones en la red de saneamiento del municipio de Arico, seleccionadas de entre las medidas contenidas en el documento “Diagnóstico y Propuestas de Actuación en materia de Saneamiento".</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>774510.76</v>
+        <v>1816937.94</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45231300, 45233252</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=V9R23eu82UwIYE3ZiZ%2BxmQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=DY9ZQkWH0O%2BLAncw3qdZkA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3939,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -3792,37 +3953,37 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Puçol</t>
+          <t>Consejo de Gobierno Insular del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Obras 1ª fase del colector unitario de la C/Alicante en Puçol.</t>
+          <t>"Red de Alcantarillado del ámbito de La Bastona", T.M.  de Santa Úrsula</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>939454.59</v>
+        <v>2057453.5</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>45231300, 45232130, 45233252</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=WKz%2F6IjRhlfXOjazN1Dw9Q%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vQGQvWXwPLudkQsA7ROvsg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3994,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -3847,37 +4008,41 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Ajuntament de Sant Feliu de Guíxols</t>
+          <t>Junta de Gobierno del Ayuntamiento de Cádiz</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>El objeto del presente contrato es la prestación del servicio de mantenimiento, conservación, inspección y limpieza de la red de alcantarillado del término municipal de Sant Feliu de Guíxols. Dentro del servicio de mantenimiento se incluyen las tareas de inspección, limpieza y conservación de la red, así como la construcción de las acometidas de terceros a la mencionada red y el mantenimiento de las acometidas de los edificios de responsabilidad municipal, restante fuera de este contrato el mantenimiento de las redes de alcantarillado de cualquier otro organismo y de las acometidas de los edificios particulares.</t>
+          <t>Suministros necesarios para la celebración del Festival Manga de Cádiz FEMANCA 2026 (4 LOTES)</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1016373.82</v>
+        <v>58016</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>manga</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>45232410, 90480000</t>
+          <t>30236000, 31211100, 31527200, 32320000, 35111300</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>https://contractaciopublica.cat/ca/detall-publicacio/6d8b7d9f-f3b1-48bc-889b-e6e04bacaf5e/300866915</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=3NalfqN%2FH1zzAq95uGTrDQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3888,7 +4053,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
@@ -3902,22 +4067,22 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Consorcio Urbanístico Leganés Tecnológico</t>
+          <t>Consejo de Administración de Aigües i Sanejament d'Elx S.A.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>LGT_2026_CO_01 Proyecto constructivo e incoación del procedimiento de contratación de las obras de finalización del colector desdoblado del arroyo Butarque en el ámbito del PP-2, centro, del Plan de Sectorización Autovía Toledo Norte del Plan General de Ordenación Urbana de Leganés (MADRID), EXPEDIENTE CO/01/2026</t>
+          <t>Obras de la Red de Ejecución del Coletor de Peña Águilas y Llano de San José. Enlaces Fases 1-4 con Colector Primario</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>784673.0699999999</v>
+        <v>1539118.58</v>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3927,12 +4092,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>45232440</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/lgt2026co01-proyecto-constructivo-e-incoacion-procedimiento-contratacion-obras</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=n8WInzjdL2PLIx6q1oPaMg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3943,7 +4108,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
@@ -3957,37 +4122,37 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Narón</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Ampliacion da rede de saneamento en A Rocha (Sedes), comprendida no Plan provincial de cooperación ás obras e servizos de competencia municipal (Plan único de concellos) POS+Adicional 2/2025</t>
+          <t>Obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>384003.04</v>
+        <v>774510.76</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>44162500, 45232400, 45232410</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=GFxBe4DrBfvL1rX3q%2FMAPA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=V9R23eu82UwIYE3ZiZ%2BxmQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3998,7 +4163,7 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
@@ -4012,37 +4177,37 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Agüimes</t>
+          <t>Alcaldía del Ayuntamiento de Puçol</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Mejora y Optimización Red de Abastecimiento de Agua de Temisas</t>
+          <t>Obras 1ª fase del colector unitario de la C/Alicante en Puçol.</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>599625.8</v>
+        <v>939454.59</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45232400</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OxfluKxhWGV6nTs9LZ9RhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=WKz%2F6IjRhlfXOjazN1Dw9Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4218,7 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -4067,37 +4232,37 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Consejería de Industria, Energía, Ciencia y Territorio</t>
+          <t>Ajuntament de Sant Feliu de Guíxols</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>OBRAG26003 Nuevo colector en Rena (Badajoz)</t>
+          <t>El objeto del presente contrato es la prestación del servicio de mantenimiento, conservación, inspección y limpieza de la red de alcantarillado del término municipal de Sant Feliu de Guíxols. Dentro del servicio de mantenimiento se incluyen las tareas de inspección, limpieza y conservación de la red, así como la construcción de las acometidas de terceros a la mencionada red y el mantenimiento de las acometidas de los edificios de responsabilidad municipal, restante fuera de este contrato el mantenimiento de las redes de alcantarillado de cualquier otro organismo y de las acometidas de los edificios particulares.</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>395041.32</v>
+        <v>1016373.82</v>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232410, 90480000</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FgAgNDFSE7aKeVWTb9Scog%3D%3D</t>
+          <t>https://contractaciopublica.cat/ca/detall-publicacio/6d8b7d9f-f3b1-48bc-889b-e6e04bacaf5e/300866915</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4273,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
@@ -4122,22 +4287,22 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de la Histórica Villa de los Realejos</t>
+          <t>Consorcio Urbanístico Leganés Tecnológico</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Contratación de obras del proyecto de "Remodelación del entorno urbano y adecuación de la red de abastecimiento en la urbanización Los Príncipes (Fase I)"</t>
+          <t>LGT_2026_CO_01 Proyecto constructivo e incoación del procedimiento de contratación de las obras de finalización del colector desdoblado del arroyo Butarque en el ámbito del PP-2, centro, del Plan de Sectorización Autovía Toledo Norte del Plan General de Ordenación Urbana de Leganés (MADRID), EXPEDIENTE CO/01/2026</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>517249.41</v>
+        <v>784673.0699999999</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4147,12 +4312,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45233222</t>
+          <t>45232440</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=VQOMAmLOSzeS81gZFETWmA%3D%3D</t>
+          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/lgt2026co01-proyecto-constructivo-e-incoacion-procedimiento-contratacion-obras</t>
         </is>
       </c>
     </row>
@@ -4177,37 +4342,37 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Administración de Limpieza y Mantenimiento de Carmona, S.L.U.</t>
+          <t>Alcaldía del Ayuntamiento de Narón</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Obras de rehabilitación de pavimentos y renovación de las redes de alcantarillado y abastecimiento de agua potable en la Barriada de Guadajoz. Fase 1</t>
+          <t>Ampliacion da rede de saneamento en A Rocha (Sedes), comprendida no Plan provincial de cooperación ás obras e servizos de competencia municipal (Plan único de concellos) POS+Adicional 2/2025</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>423938.36</v>
+        <v>384003.04</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>45232100, 45232150, 45232400, 45232410, 45233252</t>
+          <t>44162500, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bCgfi8hy24h9PLkba5eRog%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=GFxBe4DrBfvL1rX3q%2FMAPA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4232,37 +4397,37 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Confederación Hidrográfica del Miño-Sil</t>
+          <t>Alcaldía del Ayuntamiento de Agüimes</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de colectores de la red de fecales de la calle Plácido Peña. T.M. de Vilalba (Lugo) PDM MIÑO-SIL ES010_2_ALCH0SBET29UR2023</t>
+          <t>Mejora y Optimización Red de Abastecimiento de Agua de Temisas</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>675986.95</v>
+        <v>599625.8</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=0sPmJ1%2FV1fD%2Fa9DgO%2BoYKQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OxfluKxhWGV6nTs9LZ9RhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4287,37 +4452,37 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Salamanca</t>
+          <t>Consejería de Industria, Energía, Ciencia y Territorio</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Obras de Renovación de la red de distribución de agua potable en varias calles de los barrios San Cristóbal, San Esteban y Fontana y en Pizarrales Norte.</t>
+          <t>OBRAG26003 Nuevo colector en Rena (Badajoz)</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>538921.6899999999</v>
+        <v>395041.32</v>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45233200</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Nzb4BMmgaFfIGlsa0Wad%2Bw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FgAgNDFSE7aKeVWTb9Scog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4342,37 +4507,37 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Cervo</t>
+          <t>Alcaldía del Ayuntamiento de la Histórica Villa de los Realejos</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Renovación beirarrúas e rede de saneamento da avenida da Mariña, en San Ciprián</t>
+          <t>Contratación de obras del proyecto de "Remodelación del entorno urbano y adecuación de la red de abastecimiento en la urbanización Los Príncipes (Fase I)"</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>458620.35</v>
+        <v>517249.41</v>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>45232410, 45233200, 45233252</t>
+          <t>45232150, 45233222</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hQUN1x2ScH%2BLAncw3qdZkA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=VQOMAmLOSzeS81gZFETWmA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4397,22 +4562,22 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Ibdes</t>
+          <t>Consejo de Administración de Limpieza y Mantenimiento de Carmona, S.L.U.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>El proyecto de "MEJORA DE SERVICIOS Y DE PAVIMENTOS" en Ibdes, tiene por objeto diversas obras de mejora de pavimentos y de las conducciones del alcantarillado y de distribución de agua en varios tramos de las Calles Rúa y Cerro de San Lorenzo.</t>
+          <t>Obras de rehabilitación de pavimentos y renovación de las redes de alcantarillado y abastecimiento de agua potable en la Barriada de Guadajoz. Fase 1</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>346698.53</v>
+        <v>423938.36</v>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4422,12 +4587,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45232400, 45233252</t>
+          <t>45232100, 45232150, 45232400, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HF9AC8k%2B%2F3mqb7rCcv76BA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=bCgfi8hy24h9PLkba5eRog%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4452,22 +4617,22 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+          <t>Presidencia de la Confederación Hidrográfica del Miño-Sil</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>La contratación de la ejecución de las obras de pavimentación y renovación de redes calle Agustina de Aragón números 58 a 76 y adyacentes (Fase 1) y calle Agustina de Aragón números 38 a 56 y calle La Huerta núm. 1 a 9 (Fase 2)</t>
+          <t>Proyecto de colectores de la red de fecales de la calle Plácido Peña. T.M. de Vilalba (Lugo) PDM MIÑO-SIL ES010_2_ALCH0SBET29UR2023</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>545400.61</v>
+        <v>675986.95</v>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4477,12 +4642,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>45231221, 45231300, 45233252</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OvOki5I9GBJrSd8H4b2soA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=0sPmJ1%2FV1fD%2Fa9DgO%2BoYKQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4507,37 +4672,37 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Alcalde del Ayuntamiento de Alfajarin</t>
+          <t>Alcaldía del Ayuntamiento de Salamanca</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Las obras de pavimentación y renovación de redes</t>
+          <t>Obras de Renovación de la red de distribución de agua potable en varias calles de los barrios San Cristóbal, San Esteban y Fontana y en Pizarrales Norte.</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>545400</v>
+        <v>538921.6899999999</v>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>45231221, 45231300, 45233252</t>
+          <t>45231300, 45233200</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=38evUZBxaXWHCIsjvJ3rhQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Nzb4BMmgaFfIGlsa0Wad%2Bw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4562,22 +4727,22 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Alcaldía del Ayuntamiento de Cervo</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+          <t>Renovación beirarrúas e rede de saneamento da avenida da Mariña, en San Ciprián</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>533872.4</v>
+        <v>458620.35</v>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4587,12 +4752,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>45232440, 45240000</t>
+          <t>45232410, 45233200, 45233252</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HnzMWLjwbK%2B8ebB%2FXTwy0A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hQUN1x2ScH%2BLAncw3qdZkA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4617,37 +4782,37 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>AGASA-Consejo de Administración</t>
+          <t>Alcaldía del Ayuntamiento de Ibdes</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Obras de instalación de la cuarta bomba de la EBAR Santa Catalina en la red de saneamiento de AGASA</t>
+          <t>El proyecto de "MEJORA DE SERVICIOS Y DE PAVIMENTOS" en Ibdes, tiene por objeto diversas obras de mejora de pavimentos y de las conducciones del alcantarillado y de distribución de agua en varios tramos de las Calles Rúa y Cerro de San Lorenzo.</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>465242.86</v>
+        <v>346698.53</v>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>45232152</t>
+          <t>45232150, 45232400, 45233252</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso733199/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HF9AC8k%2B%2F3mqb7rCcv76BA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4672,22 +4837,22 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Artziniega-Pleno</t>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega (Fase 1)</t>
+          <t>La contratación de la ejecución de las obras de pavimentación y renovación de redes calle Agustina de Aragón números 58 a 76 y adyacentes (Fase 1) y calle Agustina de Aragón números 38 a 56 y calle La Huerta núm. 1 a 9 (Fase 2)</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>567293.62</v>
+        <v>545400.61</v>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4697,12 +4862,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45231221, 45231300, 45233252</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso31125/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=OvOki5I9GBJrSd8H4b2soA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4727,37 +4892,37 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Basauri-Alcalde</t>
+          <t>Alcalde del Ayuntamiento de Alfajarin</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Obra de reposición del muro y la red de saneamiento en la trasera de la calle Luis Petralanda 1-3 de Basauri.</t>
+          <t>Las obras de pavimentación y renovación de redes</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>469741.46</v>
+        <v>545400</v>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231221, 45231300, 45233252</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso725833/es_doc/index.html</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=38evUZBxaXWHCIsjvJ3rhQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4933,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
@@ -4782,22 +4947,22 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Dirección Gerente de Aguas Vega Sierra Elvira, S.A.</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la red de abastecimiento de las calles Salitre, Vicente Aleixandre y Málaga, y la red de saneamiento de estas dos últimas, de Atarfe (Granada).</t>
+          <t>Ejecución de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>234044.63</v>
+        <v>533872.4</v>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4807,12 +4972,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>44160000, 45200000, 45220000, 45231100, 45232100</t>
+          <t>45232440, 45240000</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=cTWFE5D8Zh5VkTabT%2FRM8A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=HnzMWLjwbK%2B8ebB%2FXTwy0A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4988,7 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -4837,37 +5002,37 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Carballo</t>
+          <t>AGASA-Consejo de Administración</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras: Red de abastecimiento de agua potable desde el lugar de Almacén al lugar de Vilar de Francos, en la parroquia de Artes (OBR 06/2026) incluída en el POS+Adicional 4/2025, 2ª Fase</t>
+          <t>Obras de instalación de la cuarta bomba de la EBAR Santa Catalina en la red de saneamiento de AGASA</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>247592.94</v>
+        <v>465242.86</v>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>45200000, 45231000, 45231300, 45232150</t>
+          <t>45232152</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=meSIPtE5fKQ7%2B9FIQYNjeQ%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso733199/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -4878,7 +5043,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -4892,37 +5057,37 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Aena. Dirección del Aeropuerto Adolfo Suárez Madrid-Barajas</t>
+          <t>Ayuntamiento de Artziniega-Pleno</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Proyecto Y Obra Acometida Red De Saneamiento Parcela Supermercado Aeroportuario</t>
+          <t>Renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega (Fase 1)</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>206300</v>
+        <v>567293.62</v>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=k1WCTiBaoektm4eBPtV6eQ%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso31125/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -4933,7 +5098,7 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
@@ -4947,37 +5112,37 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Autoridad Portuaria de la Bahía de Algeciras</t>
+          <t>Ayuntamiento de Basauri-Alcalde</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de desvio del ramal norte de la red de abastecimiento del área portuaria de Campamento</t>
+          <t>Obra de reposición del muro y la red de saneamiento en la trasera de la calle Luis Petralanda 1-3 de Basauri.</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>287137.15</v>
+        <v>469741.46</v>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232150</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=lc5tGIAbOAjmnwcj%2BxbdTg%3D%3D</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso725833/es_doc/index.html</t>
         </is>
       </c>
     </row>
@@ -5002,37 +5167,37 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Hinojosa del Duque</t>
+          <t>Dirección Gerente de Aguas Vega Sierra Elvira, S.A.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Renovación del pavimento y red de saneamiento y agua potable de la Plaza Duque de Béjar de Hinojosa del Duque.</t>
+          <t>Renovación de la red de abastecimiento de las calles Salitre, Vicente Aleixandre y Málaga, y la red de saneamiento de estas dos últimas, de Atarfe (Granada).</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>314890.08</v>
+        <v>234044.63</v>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>45220000, 45232410, 45233251, 45233252</t>
+          <t>44160000, 45200000, 45220000, 45231100, 45232100</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=tomlDPx2VWQmMOlAXxDEjw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=cTWFE5D8Zh5VkTabT%2FRM8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5057,22 +5222,22 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Torralba de Ribota</t>
+          <t>Alcaldía del Ayuntamiento de Carballo</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Obras de pavimentado de calles y renovación de redes en el término municipal de TORRALBA DE RIBOTA</t>
+          <t>Contrato de obras: Red de abastecimiento de agua potable desde el lugar de Almacén al lugar de Vilar de Francos, en la parroquia de Artes (OBR 06/2026) incluída en el POS+Adicional 4/2025, 2ª Fase</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>192375.91</v>
+        <v>247592.94</v>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5082,12 +5247,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>45111100, 45232400, 45233252, 45330000</t>
+          <t>45200000, 45231000, 45231300, 45232150</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=H%2F59EKurpZ1SYrkJkLlFdw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=meSIPtE5fKQ7%2B9FIQYNjeQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5263,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -5112,22 +5277,22 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Cretas</t>
+          <t>Aena. Dirección del Aeropuerto Adolfo Suárez Madrid-Barajas</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de acondicionamiento y renovación de conducción de abastecimiento de agua</t>
+          <t>Proyecto Y Obra Acometida Red De Saneamiento Parcela Supermercado Aeroportuario</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>118205.83</v>
+        <v>206300</v>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5137,12 +5302,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FNDtn0ZSI8RxseVhcqrkhw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=k1WCTiBaoektm4eBPtV6eQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5318,7 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
@@ -5167,37 +5332,37 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Entidad Pública Empresarial Local Centros de Arte, Cultura y Turismo de Lanzarote</t>
+          <t>Presidencia de la Autoridad Portuaria de la Bahía de Algeciras</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Obra de nueva EBAR y tubería de impulsión en La Cueva de los Verdes</t>
+          <t>Proyecto de desvio del ramal norte de la red de abastecimiento del área portuaria de Campamento</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>102536.2</v>
+        <v>287137.15</v>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232411, 45232440</t>
+          <t>45231300, 45232150</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vwVlLdPv92qcCF8sV%2BqtYA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=lc5tGIAbOAjmnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5373,7 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
@@ -5222,37 +5387,37 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+          <t>Alcaldía del Ayuntamiento de Hinojosa del Duque</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Renovación de tubería de distribución en el vial público C/ Vicent Serra y actuaciones complementarias en el sistema de abastecimiento urbano de Sant Miquel de Balansat</t>
+          <t>Renovación del pavimento y red de saneamiento y agua potable de la Plaza Duque de Béjar de Hinojosa del Duque.</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>96500.2</v>
+        <v>314890.08</v>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+          <t>45220000, 45232410, 45233251, 45233252</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=c3vjWc0VQQ0aF6cS8TCh%2FA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=tomlDPx2VWQmMOlAXxDEjw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5428,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -5277,22 +5442,22 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
+          <t>Pleno del Ayuntamiento de Torralba de Ribota</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Renovación de tubería de distribución en Plaza España y Calle Mossèn Vicent Ferrer i Guasch, con actuaciones complementarias en el sistema de abastecimiento urbano de Sant Joan de Labritja</t>
+          <t>Obras de pavimentado de calles y renovación de redes en el término municipal de TORRALBA DE RIBOTA</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>125890</v>
+        <v>192375.91</v>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5302,12 +5467,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
+          <t>45111100, 45232400, 45233252, 45330000</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=2yr%2BUKjzV%2BGFlFRHfEzEaw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=H%2F59EKurpZ1SYrkJkLlFdw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5332,37 +5497,37 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Xunta de Goberno Local del Ayuntamiento de Boiro</t>
+          <t>Pleno del Ayuntamiento de Cretas</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Contratación para a execución da obra de Renovación de tramo de tubería de impulsión á estación de tratamento de auga potable (ETAP) de Boiro, mediante procedemento aberto e TRAMITACIÓN ANTICIPADA (DA 3.2 LCSP) vinculada subvención solicitada Augas de Galicia (DOG número 90 do 18 de maio de 2025) cofinanciada fondos FEDER programa 2021-2027(código proc. AU301E)</t>
+          <t>Proyecto de acondicionamiento y renovación de conducción de abastecimiento de agua</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>79632.66</v>
+        <v>118205.83</v>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=g3pTkEh1QTyS81gZFETWmA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FNDtn0ZSI8RxseVhcqrkhw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5387,37 +5552,37 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Cáceres</t>
+          <t>Entidad Pública Empresarial Local Centros de Arte, Cultura y Turismo de Lanzarote</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Renovación en la Red de Saneamiento de tramo en Calles Islas Baleares, Pedro Romero Mendoza y Arsenio Gallego, Recrecido de Pozos de Saneamiento en Parcela Municipal y Renovación de Acometida de Saneamiento del Camping Municipal de Cáceres.</t>
+          <t>Obra de nueva EBAR y tubería de impulsión en La Cueva de los Verdes</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>82975.21000000001</v>
+        <v>102536.2</v>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231300, 45232411, 45232440</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=nVZ97Q1pak%2FkY6rls5tG9A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=vwVlLdPv92qcCF8sV%2BqtYA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5442,22 +5607,22 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Villablino</t>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obra de renovación de red de abastecimiento y aceras de la Calle Leitariegos en Villablino</t>
+          <t>Renovación de tubería de distribución en el vial público C/ Vicent Serra y actuaciones complementarias en el sistema de abastecimiento urbano de Sant Miquel de Balansat</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>147377.86</v>
+        <v>96500.2</v>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5467,12 +5632,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>45232150, 45233222</t>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2Fcvza%2BgevtBWhbmkna2nXQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=c3vjWc0VQQ0aF6cS8TCh%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5497,37 +5662,37 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Alginet</t>
+          <t>Alcaldía del Ayuntamiento de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la red de alcantarillado de la urbanización San Patricio d'Alginet (Fase I)</t>
+          <t>Renovación de tubería de distribución en Plaza España y Calle Mossèn Vicent Ferrer i Guasch, con actuaciones complementarias en el sistema de abastecimiento urbano de Sant Joan de Labritja</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>150364.75</v>
+        <v>125890</v>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>45200000, 45231300, 45232150, 45232400, 45232410</t>
+          <t>45112100, 45231300, 45232150, 45232410, 45233222</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=74A3N79XrwAeC9GJQOEBkQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=2yr%2BUKjzV%2BGFlFRHfEzEaw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5552,37 +5717,37 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Miengo</t>
+          <t>Xunta de Goberno Local del Ayuntamiento de Boiro</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Renovación de la Red General de Abastecimiento en Avenida de Los Menicenses de Miengo en término municipal de Miengo</t>
+          <t>Contratación para a execución da obra de Renovación de tramo de tubería de impulsión á estación de tratamento de auga potable (ETAP) de Boiro, mediante procedemento aberto e TRAMITACIÓN ANTICIPADA (DA 3.2 LCSP) vinculada subvención solicitada Augas de Galicia (DOG número 90 do 18 de maio de 2025) cofinanciada fondos FEDER programa 2021-2027(código proc. AU301E)</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>80603.17</v>
+        <v>79632.66</v>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FfuggmFUPMKAAM7L03kM8A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=g3pTkEh1QTyS81gZFETWmA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5772,22 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Alcalà de Xivert</t>
+          <t>Alcaldía del Ayuntamiento de Cáceres</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Obras de mejoras hidráulicas en la red de saneamiento de Alcalà de Xivert-Alcossebre</t>
+          <t>Renovación en la Red de Saneamiento de tramo en Calles Islas Baleares, Pedro Romero Mendoza y Arsenio Gallego, Recrecido de Pozos de Saneamiento en Parcela Municipal y Renovación de Acometida de Saneamiento del Camping Municipal de Cáceres.</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>100541.82</v>
+        <v>82975.21000000001</v>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5637,7 +5802,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=a%2FsgtfkOGkAUqXM96WStVA%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=nVZ97Q1pak%2FkY6rls5tG9A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5662,41 +5827,37 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Consejería Insular de Área de Cooperación Municipal y Vivienda del Cabildo Insular de Tenerife</t>
+          <t>Alcaldía del Ayuntamiento de Villablino</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>El objeto del contrato de servicios será la REDACCIÓN DEL PROYECTO y DIRECCIÓN DE LA OBRA denominada "REFORMA DE LA RED DE SANEAMIENTO DE LA CALETA DE INTERIÁN, FASE II", en el municipio de Garachico, incluidas en el Plan Insular de Cooperación a las obras y servicios de competencia municipal 2022-2026.</t>
+          <t>Contrato de obra de renovación de red de abastecimiento y aceras de la Calle Leitariegos en Villablino</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>99971.42</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>147377.86</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>71000000, 71240000</t>
+          <t>45232150, 45233222</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=P0CRmBEuH2%2Fmnwcj%2BxbdTg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=%2Fcvza%2BgevtBWhbmkna2nXQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5721,37 +5882,37 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Consell</t>
+          <t>Alcaldía del Ayuntamiento de Alginet</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras de renovación de la red de agua potable y mejora del firme del camino de Son Biel.</t>
+          <t>Renovación de la red de alcantarillado de la urbanización San Patricio d'Alginet (Fase I)</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>107187.43</v>
+        <v>150364.75</v>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>45232100, 45232150</t>
+          <t>45200000, 45231300, 45232150, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=ea7jddmClrhVq4S9zvaQpQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=74A3N79XrwAeC9GJQOEBkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5776,37 +5937,37 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Baena</t>
+          <t>Alcaldía del Ayuntamiento de Miengo</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Obras de mejora y ampliación de la red de saneamiento de la calle Matadero y confluencias de Avda Cañete de las Torres, calle Demetrio de los Ríos y calle Sargento Domingo Argudo.</t>
+          <t>Renovación de la Red General de Abastecimiento en Avenida de Los Menicenses de Miengo en término municipal de Miengo</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>69567.39999999999</v>
+        <v>80603.17</v>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>45112000, 45232400, 45232410</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=iNYtiIP2jyQeC9GJQOEBkQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=FfuggmFUPMKAAM7L03kM8A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5831,37 +5992,37 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Comisión ejecutiva del Consejo de Administración de la Empresa Municipal de Transportes de Fuenlabrada, S.A.</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Alcalà de Xivert</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Obras para la mejora integral de la red de saneamiento interior y construcción de un aseo auxiliar exterior en la campa de la EMTF</t>
+          <t>Obras de mejoras hidráulicas en la red de saneamiento de Alcalà de Xivert-Alcossebre</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>102721.88</v>
+        <v>100541.82</v>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>45215500, 45232400, 45232410, 45233252</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=eVV8%2BC8olRV4zIRvjBVCSw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=a%2FsgtfkOGkAUqXM96WStVA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5886,16 +6047,16 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Área de Fomento de la Diputación Provincial de Badajoz</t>
+          <t>Consejería Insular de Área de Cooperación Municipal y Vivienda del Cabildo Insular de Tenerife</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la redacción del proyecto de ejecución, dirección de obras y coordinación de seguridad y salud, por lotes, para las obras de  mejora red de abastecimiento en varias localidades de la provincia de Badajoz. Cofinanciado al 85% por FEDER a través del Programa Plurirregional de España 2021-2027</t>
+          <t>El objeto del contrato de servicios será la REDACCIÓN DEL PROYECTO y DIRECCIÓN DE LA OBRA denominada "REFORMA DE LA RED DE SANEAMIENTO DE LA CALETA DE INTERIÁN, FASE II", en el municipio de Garachico, incluidas en el Plan Insular de Cooperación a las obras y servicios de competencia municipal 2022-2026.</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>112019.15</v>
+        <v>99971.42</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -5905,22 +6066,22 @@
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>71310000</t>
+          <t>71000000, 71240000</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=By3FKGFakezVGIpKDxgsAQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=P0CRmBEuH2%2Fmnwcj%2BxbdTg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -5945,37 +6106,37 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Alcaldia del Ayuntamiento de Argamasilla de Calatrava</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Consell</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Mejora de la red de abastecimiento de agua potable en el municipio de Argamasilla de Calatrava.</t>
+          <t>Contrato de obras de renovación de la red de agua potable y mejora del firme del camino de Son Biel.</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>88836.67999999999</v>
+        <v>107187.43</v>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45232100, 45232150</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=16Y%2BH5iLq9GP%2Bo96UAV7cQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=ea7jddmClrhVq4S9zvaQpQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6000,37 +6161,37 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Dirección Gerente de Aguas de Lorca, S.A.</t>
+          <t>Alcaldía del Ayuntamiento de Baena</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación de redes municipales de abastecimiento de agua potable en el T.M. de Lorca</t>
+          <t>Obras de mejora y ampliación de la red de saneamiento de la calle Matadero y confluencias de Avda Cañete de las Torres, calle Demetrio de los Ríos y calle Sargento Domingo Argudo.</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>117149.12</v>
+        <v>69567.39999999999</v>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>45231100, 45232100, 45232150, 45232151</t>
+          <t>45112000, 45232400, 45232410</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=7ek7iek2RL3%2Fa9DgO%2BoYKQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=iNYtiIP2jyQeC9GJQOEBkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6055,37 +6216,37 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Canena</t>
+          <t>Comisión ejecutiva del Consejo de Administración de la Empresa Municipal de Transportes de Fuenlabrada, S.A.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Actuación de emergencia en la red de saneamiento en esquina calle Altozano y calle Iglesia, Canena (Jaén)</t>
+          <t>Obras para la mejora integral de la red de saneamiento interior y construcción de un aseo auxiliar exterior en la campa de la EMTF</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>82639.3</v>
+        <v>102721.88</v>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45215500, 45232400, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=yETWMHlcJJ0QyBAnWzHfCg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=eVV8%2BC8olRV4zIRvjBVCSw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6257,7 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
@@ -6110,37 +6271,41 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Valdemorales</t>
+          <t>Área de Fomento de la Diputación Provincial de Badajoz</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras correspondientes exclusivamente a la fase 1 conducción general del proyecto general de "modernización de la red de abastecimiento del municipio de  Valdemorales (Cáceres)</t>
+          <t>Asistencia técnica para la redacción del proyecto de ejecución, dirección de obras y coordinación de seguridad y salud, por lotes, para las obras de  mejora red de abastecimiento en varias localidades de la provincia de Badajoz. Cofinanciado al 85% por FEDER a través del Programa Plurirregional de España 2021-2027</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>44037.27</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
+        <v>112019.15</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>45231300, 45232150, 45233200, 45240000, 45252126</t>
+          <t>71310000</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=blNQxGZAd9JJ8Trn0ZPzLw%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=By3FKGFakezVGIpKDxgsAQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6316,7 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
@@ -6165,37 +6330,37 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Alcaldia del Ayuntamiento de Argamasilla de Calatrava</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Dirección de las obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
+          <t>Mejora de la red de abastecimiento de agua potable en el municipio de Argamasilla de Calatrava.</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>61960.86</v>
+        <v>88836.67999999999</v>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>71300000, 71322000, 71520000</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=MCV%2BAUHsDWnCfVQHDepjGQ%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=16Y%2BH5iLq9GP%2Bo96UAV7cQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6371,7 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
@@ -6220,37 +6385,37 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
+          <t>Dirección Gerente de Aguas de Lorca, S.A.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Dirección de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
+          <t>Obras de renovación de redes municipales de abastecimiento de agua potable en el T.M. de Lorca</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>44610.5</v>
+        <v>117149.12</v>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>71300000, 71322000, 71520000</t>
+          <t>45231100, 45232100, 45232150, 45232151</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=F%2FUx5m7rtlu8ebB%2FXTwy0A%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=7ek7iek2RL3%2Fa9DgO%2BoYKQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6426,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
@@ -6275,37 +6440,37 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de La Solana</t>
+          <t>Alcaldía del Ayuntamiento de Canena</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Obras de Renovación de redes de abastecimiento en Calle Molinos de Viento, de La Solana (Ciudad Real)</t>
+          <t>Actuación de emergencia en la red de saneamiento en esquina calle Altozano y calle Iglesia, Canena (Jaén)</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>61709.77</v>
+        <v>82639.3</v>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45231300</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hwqCatsJl8gS7pcxhTeWOg%3D%3D</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=yETWMHlcJJ0QyBAnWzHfCg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6330,37 +6495,37 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Ente Público Empresarial Augas de Galicia</t>
+          <t>Alcaldía del Ayuntamiento de Valdemorales</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>AUG-2026-0032: Obra de ampliación y mejora de la red de saneamiento integral del municipio. Saneamiento del Camino de la Torroeira. Parroquia de Louredo. Mos (Pontevedra). Actuación cofinanciada por la Unión Europea con el Fondo Europeo Agrícola de Desarrollo Rural (Feader) en un 60% del gasto elegible en el marco del Plan estratégico de la política agrícola común 2023_2027 (PEPAC) en Galicia.</t>
+          <t>Ejecución de las obras correspondientes exclusivamente a la fase 1 conducción general del proyecto general de "modernización de la red de abastecimiento del municipio de  Valdemorales (Cáceres)</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>63904.44</v>
+        <v>44037.27</v>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>PUB</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>45232410</t>
+          <t>45231300, 45232150, 45233200, 45240000, 45252126</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratosdegalicia.gal/licitacion?N=827669</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=blNQxGZAd9JJ8Trn0ZPzLw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6385,33 +6550,37 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Comisión Permanente de la Mancomunidad de Valdizarbe - Izarbeibarko Mankomunitatea</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Obras de renovación del colector de saneamiento de la Calle Santa María (campo de fútbol) en Obanos</t>
+          <t>Dirección de las obras de reparación del colector general 6 en la rotonda de acceso a la V- 21 perteneciente al sistema de saneamiento de La Pobla de Farnals, en el municipio de La Pobla de Farnals y en El Puig de Santa María (Valencia)</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>51496.63</v>
+        <v>61960.86</v>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>ADJ</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>45112000, 45231300, 45232410, 45233252</t>
+          <t>71300000, 71322000, 71520000</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=8086&amp;Ticket=2608261225566A4631E8</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=MCV%2BAUHsDWnCfVQHDepjGQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6436,37 +6605,37 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Mancomunidad de Mairaga</t>
+          <t>Vicepresidencia del Consejo de Administración de la Entidad Pública de Saneamiento de Aguas Residuales de la Comunidad Valenciana</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto y dirección facultativa de la obra de Pavimentación y renovación de redes de calles Barranco Salado, La Estanca y Bardenas Reales de Caparroso</t>
+          <t>Dirección de las obras de reparación urgente por la rotura del ramal C del colector general de la EDAR OBVA a su paso por el Barranco de Ratils en Vila-Real (Castellón).</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>43017.16</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>44610.5</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>71240000</t>
+          <t>71300000, 71322000, 71520000</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2608031429198E3AD3EC</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=F%2FUx5m7rtlu8ebB%2FXTwy0A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6491,33 +6660,37 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Baztan</t>
+          <t>Alcaldía del Ayuntamiento de La Solana</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>conexión a la red de saneamiento del barrio de Etxerri de Gartzain en el municipio de Baztan</t>
+          <t>Obras de Renovación de redes de abastecimiento en Calle Molinos de Viento, de La Solana (Ciudad Real)</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>41206.09</v>
+        <v>61709.77</v>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>45231100, 45232150</t>
+          <t>45232150</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2607211228565F80EFF5</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=hwqCatsJl8gS7pcxhTeWOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -6542,26 +6715,22 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Portugalete -Alcalde</t>
+          <t>Ente Público Empresarial Augas de Galicia</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la redacción del proyecto de renovación del colector H de la calle Miralrío de Portugalete.</t>
+          <t>AUG-2026-0032: Obra de ampliación y mejora de la red de saneamiento integral del municipio. Saneamiento del Camino de la Torroeira. Parroquia de Louredo. Mos (Pontevedra). Actuación cofinanciada por la Unión Europea con el Fondo Europeo Agrícola de Desarrollo Rural (Feader) en un 60% del gasto elegible en el marco del Plan estratégico de la política agrícola común 2023_2027 (PEPAC) en Galicia.</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>63904.44</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6571,12 +6740,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>71242000</t>
+          <t>45232410</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso702799/es_doc/index.html</t>
+          <t>https://www.contratosdegalicia.gal/licitacion?N=827669</t>
         </is>
       </c>
     </row>
@@ -6601,37 +6770,33 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Diputación Provincial de Palencia</t>
+          <t>Comisión Permanente de la Mancomunidad de Valdizarbe - Izarbeibarko Mankomunitatea</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Renovación del Último Tramo de la Red de Saneamiento, Margen Izquierdo de la Calle Extramuros en San Cebrián de Campos</t>
+          <t>Obras de renovación del colector de saneamiento de la Calle Santa María (campo de fútbol) en Obanos</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>46232.23</v>
+        <v>51496.63</v>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+      <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>ADJ</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>45112000, 45231300, 45232410, 45233252</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=8lAFGG5SIx9%2BF6L2uCfUWg%3D%3D</t>
+          <t>https://hacienda.navarra.es/sicpportal/ctaDatosAdjudicacion.aspx?cod=8086&amp;Ticket=2608261225566A4631E8</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6807,7 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
@@ -6656,16 +6821,16 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Artziniega-Alcalde</t>
+          <t>Presidencia de la Mancomunidad de Mairaga</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Redacción del Proyecto y Dirección Facultativa para las obras de renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega- Fase II</t>
+          <t>Redacción de proyecto y dirección facultativa de la obra de Pavimentación y renovación de redes de calles Barranco Salado, La Estanca y Bardenas Reales de Caparroso</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>19355</v>
+        <v>43017.16</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -6673,14 +6838,10 @@
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-08</t>
-        </is>
-      </c>
+      <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -6690,7 +6851,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso398838/es_doc/index.html</t>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2608031429198E3AD3EC</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6862,7 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
@@ -6715,24 +6876,20 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Torre Pacheco</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Baztan</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Renovación de red de saneamiento y abastecimiento en el entorno e interior del Colegio Hernández Ardieta en Roldán.</t>
+          <t>conexión a la red de saneamiento del barrio de Etxerri de Gartzain en el municipio de Baztan</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>33430.04</v>
+        <v>41206.09</v>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr">
         <is>
           <t>EV</t>
@@ -6740,12 +6897,12 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>45231300</t>
+          <t>45231100, 45232150</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Y9IK1q%2Bwcyz10HRJw8TEnQ%3D%3D</t>
+          <t>https://hacienda.navarra.es/sicpportal/mtoAnunciosModalidad.aspx?cod=2607211228565F80EFF5</t>
         </is>
       </c>
     </row>
@@ -6756,11 +6913,11 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6770,38 +6927,52 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Ajuntament de Sant Feliu de Guíxols</t>
+          <t>Ayuntamiento de Portugalete -Alcalde</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>España – Servicios de gestión de alcantarillados – Contrato para el servicio de mantenimiento, conservación y reposiciones o actuaciones de la red de alcantarillado y pluviales y elementos auxiliares dentro del término municipal de Sant Feliu de Guíxols</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="inlineStr"/>
+          <t>Asistencia técnica para la redacción del proyecto de renovación del colector H de la calle Miralrío de Portugalete.</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>ADJ</t>
+        </is>
+      </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>90480000, 90480000</t>
+          <t>71242000</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu/es/notice/-/detail/593652-2026</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso702799/es_doc/index.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
@@ -6815,140 +6986,354 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>AQUAVALL</t>
+          <t>Presidencia de la Diputación Provincial de Palencia</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+          <t>Renovación del Último Tramo de la Red de Saneamiento, Margen Izquierdo de la Calle Extramuros en San Cebrián de Campos</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>180000</v>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+        <v>46232.23</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>PUB</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>71322000</t>
+          <t>45232400</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>https://contrataciondelestado.es/</t>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=8lAFGG5SIx9%2BF6L2uCfUWg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Águas e Energia do Porto</t>
+          <t>Ayuntamiento de Artziniega-Alcalde</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+          <t>Redacción del Proyecto y Dirección Facultativa para las obras de renovación de las tuberías de fibrocemento existentes en la red de abastecimiento de Artziniega- Fase II</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>sem vala</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
+        <v>19355</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>45232400</t>
+          <t>71240000</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu/</t>
+          <t>https://www.contratacion.euskadi.eus/webkpe00-kpeperfi/es/contenidos/anuncio_contratacion/expjaso398838/es_doc/index.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>PLACSP</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>SIMAS de Oeiras e Amadora</t>
+          <t>Alcaldía del Ayuntamiento de Torre Pacheco</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+          <t>Renovación de red de saneamiento y abastecimiento en el entorno e interior del Colegio Hernández Ardieta en Roldán.</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>890000</v>
+        <v>33430.04</v>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>45231300</t>
+        </is>
+      </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
+          <t>https://contrataciondelestado.es/wps/poc?uri=deeplink:detalle_licitacion&amp;idEvl=Y9IK1q%2Bwcyz10HRJw8TEnQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Ajuntament de Sant Feliu de Guíxols</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>España – Servicios de gestión de alcantarillados – Contrato para el servicio de mantenimiento, conservación y reposiciones o actuaciones de la red de alcantarillado y pluviales y elementos auxiliares dentro del término municipal de Sant Feliu de Guíxols</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>90480000, 90480000</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/es/notice/-/detail/593652-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>PLACSP</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>AQUAVALL</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de renovación de la red de abastecimiento en alta, tramo norte</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>PUB</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>71322000</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>https://contrataciondelestado.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Águas e Energia do Porto</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Empreitada de reabilitação sem vala de coletores de águas residuais na zona ribeirinha</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>sem vala</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>45232400</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>SIMAS de Oeiras e Amadora</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Renovação de condutas de abastecimento em fibrocimento — várias freguesias</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>890000</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
           <t>https://www.base.gov.pt/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M115"/>
+  <autoFilter ref="A1:M119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Radar_Detecciones.xlsx
+++ b/data/Radar_Detecciones.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Todas las detecciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alertas nuevas'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todas las detecciones'!$A$1:$M$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -528,173 +528,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Obras del “Proyecto de Renovación de la Red de Saneamiento en el Municipio de Chapinería. Fase I (Plan Sanea 2500)”. CYII 2026/16</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>4728984.64</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/obras-proyecto-renovacion-red-saneamiento-municipio-chapineria-fase-i-plan-sanea</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Contrato de Obras del Proyecto de Renovación de la Red de Saneamiento en el municipio de Corpa. Fase I (Plan Sanea 2500).”. CYII2026/30</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>2276647.78</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-corpa-fase-i-plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>PLACSP</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Canal de Isabel II</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Contrato de Obras del “Proyecto de Renovación de la Red de Saneamiento en el municipio de Villar del Olmo. Fase I (Plan Sanea 2500)”. CYII 2025/25</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1341805.74</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>45232410</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://contratos-publicos.comunidad.madrid/contrato-publico/contrato-obras-proyecto-renovacion-red-saneamiento-municipio-villar-olmo-fase-i</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M4"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
